--- a/output/version3/test/15-10/MARL/IL/RL-RL with pt (+comm+it)/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-10/MARL/IL/RL-RL with pt (+comm+it)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>552</v>
+        <v>708</v>
       </c>
       <c r="C2" t="n">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="D2" t="n">
         <v>546</v>
       </c>
       <c r="E2" t="n">
-        <v>490</v>
+        <v>655</v>
       </c>
       <c r="F2" t="n">
-        <v>609</v>
+        <v>529</v>
       </c>
       <c r="G2" t="n">
-        <v>640</v>
+        <v>543</v>
       </c>
       <c r="H2" t="n">
-        <v>629</v>
+        <v>670</v>
       </c>
       <c r="I2" t="n">
-        <v>599</v>
+        <v>627</v>
       </c>
       <c r="J2" t="n">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="K2" t="n">
-        <v>557</v>
+        <v>605</v>
       </c>
       <c r="L2" t="n">
-        <v>571.7</v>
+        <v>595.9</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>602</v>
+        <v>519</v>
       </c>
       <c r="C3" t="n">
-        <v>629</v>
+        <v>791</v>
       </c>
       <c r="D3" t="n">
-        <v>551</v>
+        <v>686</v>
       </c>
       <c r="E3" t="n">
-        <v>608</v>
+        <v>632</v>
       </c>
       <c r="F3" t="n">
-        <v>610</v>
+        <v>720</v>
       </c>
       <c r="G3" t="n">
+        <v>558</v>
+      </c>
+      <c r="H3" t="n">
+        <v>761</v>
+      </c>
+      <c r="I3" t="n">
+        <v>577</v>
+      </c>
+      <c r="J3" t="n">
         <v>579</v>
       </c>
-      <c r="H3" t="n">
-        <v>564</v>
-      </c>
-      <c r="I3" t="n">
-        <v>615</v>
-      </c>
-      <c r="J3" t="n">
-        <v>570</v>
-      </c>
       <c r="K3" t="n">
-        <v>624</v>
+        <v>533</v>
       </c>
       <c r="L3" t="n">
-        <v>595.2</v>
+        <v>635.6</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>629</v>
+        <v>553</v>
       </c>
       <c r="C4" t="n">
-        <v>599</v>
+        <v>653</v>
       </c>
       <c r="D4" t="n">
+        <v>614</v>
+      </c>
+      <c r="E4" t="n">
+        <v>647</v>
+      </c>
+      <c r="F4" t="n">
+        <v>772</v>
+      </c>
+      <c r="G4" t="n">
+        <v>650</v>
+      </c>
+      <c r="H4" t="n">
         <v>638</v>
       </c>
-      <c r="E4" t="n">
-        <v>658</v>
-      </c>
-      <c r="F4" t="n">
-        <v>592</v>
-      </c>
-      <c r="G4" t="n">
-        <v>603</v>
-      </c>
-      <c r="H4" t="n">
-        <v>570</v>
-      </c>
       <c r="I4" t="n">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="J4" t="n">
-        <v>635</v>
+        <v>547</v>
       </c>
       <c r="K4" t="n">
-        <v>661</v>
+        <v>558</v>
       </c>
       <c r="L4" t="n">
-        <v>621.3</v>
+        <v>624.8</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>744</v>
+        <v>679</v>
       </c>
       <c r="C5" t="n">
-        <v>638</v>
+        <v>704</v>
       </c>
       <c r="D5" t="n">
-        <v>586</v>
+        <v>659</v>
       </c>
       <c r="E5" t="n">
-        <v>679</v>
+        <v>568</v>
       </c>
       <c r="F5" t="n">
-        <v>579</v>
+        <v>686</v>
       </c>
       <c r="G5" t="n">
-        <v>663</v>
+        <v>637</v>
       </c>
       <c r="H5" t="n">
-        <v>641</v>
+        <v>689</v>
       </c>
       <c r="I5" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="J5" t="n">
-        <v>646</v>
+        <v>659</v>
       </c>
       <c r="K5" t="n">
-        <v>611</v>
+        <v>677</v>
       </c>
       <c r="L5" t="n">
-        <v>638.8</v>
+        <v>656.2</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>597</v>
+        <v>630</v>
       </c>
       <c r="C6" t="n">
+        <v>636</v>
+      </c>
+      <c r="D6" t="n">
         <v>563</v>
       </c>
-      <c r="D6" t="n">
-        <v>614</v>
-      </c>
       <c r="E6" t="n">
-        <v>622</v>
+        <v>580</v>
       </c>
       <c r="F6" t="n">
-        <v>543</v>
+        <v>575</v>
       </c>
       <c r="G6" t="n">
+        <v>613</v>
+      </c>
+      <c r="H6" t="n">
+        <v>658</v>
+      </c>
+      <c r="I6" t="n">
+        <v>607</v>
+      </c>
+      <c r="J6" t="n">
+        <v>609</v>
+      </c>
+      <c r="K6" t="n">
         <v>617</v>
       </c>
-      <c r="H6" t="n">
-        <v>558</v>
-      </c>
-      <c r="I6" t="n">
-        <v>611</v>
-      </c>
-      <c r="J6" t="n">
-        <v>552</v>
-      </c>
-      <c r="K6" t="n">
-        <v>670</v>
-      </c>
       <c r="L6" t="n">
-        <v>594.7</v>
+        <v>608.8</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>682</v>
+        <v>573</v>
       </c>
       <c r="C7" t="n">
-        <v>598</v>
+        <v>657</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>571</v>
       </c>
       <c r="E7" t="n">
-        <v>549</v>
+        <v>670</v>
       </c>
       <c r="F7" t="n">
-        <v>600</v>
+        <v>554</v>
       </c>
       <c r="G7" t="n">
-        <v>678</v>
+        <v>545</v>
       </c>
       <c r="H7" t="n">
-        <v>539</v>
+        <v>622</v>
       </c>
       <c r="I7" t="n">
-        <v>637</v>
+        <v>572</v>
       </c>
       <c r="J7" t="n">
-        <v>551</v>
+        <v>573</v>
       </c>
       <c r="K7" t="n">
-        <v>627</v>
+        <v>547</v>
       </c>
       <c r="L7" t="n">
-        <v>612.2</v>
+        <v>588.4</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="C8" t="n">
-        <v>612</v>
+        <v>569</v>
       </c>
       <c r="D8" t="n">
-        <v>576</v>
+        <v>628</v>
       </c>
       <c r="E8" t="n">
+        <v>643</v>
+      </c>
+      <c r="F8" t="n">
+        <v>549</v>
+      </c>
+      <c r="G8" t="n">
+        <v>579</v>
+      </c>
+      <c r="H8" t="n">
+        <v>514</v>
+      </c>
+      <c r="I8" t="n">
         <v>621</v>
       </c>
-      <c r="F8" t="n">
-        <v>557</v>
-      </c>
-      <c r="G8" t="n">
-        <v>620</v>
-      </c>
-      <c r="H8" t="n">
-        <v>546</v>
-      </c>
-      <c r="I8" t="n">
-        <v>637</v>
-      </c>
       <c r="J8" t="n">
-        <v>594</v>
+        <v>562</v>
       </c>
       <c r="K8" t="n">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="L8" t="n">
-        <v>593.8</v>
+        <v>584.9</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>515</v>
+        <v>609</v>
       </c>
       <c r="C9" t="n">
-        <v>534</v>
+        <v>591</v>
       </c>
       <c r="D9" t="n">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="E9" t="n">
-        <v>536</v>
+        <v>643</v>
       </c>
       <c r="F9" t="n">
-        <v>572</v>
+        <v>503</v>
       </c>
       <c r="G9" t="n">
-        <v>637</v>
+        <v>539</v>
       </c>
       <c r="H9" t="n">
-        <v>689</v>
+        <v>563</v>
       </c>
       <c r="I9" t="n">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="J9" t="n">
+        <v>585</v>
+      </c>
+      <c r="K9" t="n">
         <v>591</v>
       </c>
-      <c r="K9" t="n">
-        <v>520</v>
-      </c>
       <c r="L9" t="n">
-        <v>571.8</v>
+        <v>578.4</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>643</v>
+        <v>774</v>
       </c>
       <c r="C10" t="n">
-        <v>682</v>
+        <v>696</v>
       </c>
       <c r="D10" t="n">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="E10" t="n">
-        <v>788</v>
+        <v>652</v>
       </c>
       <c r="F10" t="n">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="G10" t="n">
-        <v>698</v>
+        <v>675</v>
       </c>
       <c r="H10" t="n">
-        <v>751</v>
+        <v>639</v>
       </c>
       <c r="I10" t="n">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="J10" t="n">
-        <v>695</v>
+        <v>716</v>
       </c>
       <c r="K10" t="n">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="L10" t="n">
-        <v>700.1</v>
+        <v>689</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>641</v>
+        <v>594</v>
       </c>
       <c r="C11" t="n">
-        <v>633</v>
+        <v>670</v>
       </c>
       <c r="D11" t="n">
-        <v>666</v>
+        <v>595</v>
       </c>
       <c r="E11" t="n">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F11" t="n">
-        <v>611</v>
+        <v>638</v>
       </c>
       <c r="G11" t="n">
-        <v>595</v>
+        <v>647</v>
       </c>
       <c r="H11" t="n">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="I11" t="n">
-        <v>617</v>
+        <v>589</v>
       </c>
       <c r="J11" t="n">
-        <v>662</v>
+        <v>704</v>
       </c>
       <c r="K11" t="n">
-        <v>585</v>
+        <v>753</v>
       </c>
       <c r="L11" t="n">
-        <v>623.5</v>
+        <v>640.4</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="C12" t="n">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="D12" t="n">
-        <v>622</v>
+        <v>519</v>
       </c>
       <c r="E12" t="n">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="F12" t="n">
-        <v>636</v>
+        <v>598</v>
       </c>
       <c r="G12" t="n">
-        <v>582</v>
+        <v>667</v>
       </c>
       <c r="H12" t="n">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="I12" t="n">
+        <v>641</v>
+      </c>
+      <c r="J12" t="n">
         <v>561</v>
       </c>
-      <c r="J12" t="n">
-        <v>639</v>
-      </c>
       <c r="K12" t="n">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="L12" t="n">
-        <v>623</v>
+        <v>621.9</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>642</v>
+        <v>816</v>
       </c>
       <c r="C13" t="n">
-        <v>830</v>
+        <v>813</v>
       </c>
       <c r="D13" t="n">
-        <v>592</v>
+        <v>705</v>
       </c>
       <c r="E13" t="n">
-        <v>843</v>
+        <v>879</v>
       </c>
       <c r="F13" t="n">
-        <v>798</v>
+        <v>662</v>
       </c>
       <c r="G13" t="n">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="H13" t="n">
+        <v>724</v>
+      </c>
+      <c r="I13" t="n">
+        <v>736</v>
+      </c>
+      <c r="J13" t="n">
+        <v>736</v>
+      </c>
+      <c r="K13" t="n">
         <v>789</v>
       </c>
-      <c r="I13" t="n">
-        <v>836</v>
-      </c>
-      <c r="J13" t="n">
-        <v>799</v>
-      </c>
-      <c r="K13" t="n">
-        <v>869</v>
-      </c>
       <c r="L13" t="n">
-        <v>776.2</v>
+        <v>765.3</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>674</v>
+        <v>642</v>
       </c>
       <c r="C14" t="n">
-        <v>793</v>
+        <v>524</v>
       </c>
       <c r="D14" t="n">
-        <v>661</v>
+        <v>574</v>
       </c>
       <c r="E14" t="n">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F14" t="n">
-        <v>724</v>
+        <v>689</v>
       </c>
       <c r="G14" t="n">
-        <v>562</v>
+        <v>760</v>
       </c>
       <c r="H14" t="n">
-        <v>704</v>
+        <v>731</v>
       </c>
       <c r="I14" t="n">
-        <v>603</v>
+        <v>679</v>
       </c>
       <c r="J14" t="n">
-        <v>617</v>
+        <v>657</v>
       </c>
       <c r="K14" t="n">
-        <v>744</v>
+        <v>646</v>
       </c>
       <c r="L14" t="n">
-        <v>669.6</v>
+        <v>651.4</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>631</v>
+        <v>665</v>
       </c>
       <c r="C15" t="n">
-        <v>681</v>
+        <v>610</v>
       </c>
       <c r="D15" t="n">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="E15" t="n">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F15" t="n">
+        <v>620</v>
+      </c>
+      <c r="G15" t="n">
+        <v>756</v>
+      </c>
+      <c r="H15" t="n">
+        <v>717</v>
+      </c>
+      <c r="I15" t="n">
+        <v>695</v>
+      </c>
+      <c r="J15" t="n">
+        <v>620</v>
+      </c>
+      <c r="K15" t="n">
         <v>591</v>
       </c>
-      <c r="G15" t="n">
-        <v>693</v>
-      </c>
-      <c r="H15" t="n">
-        <v>685</v>
-      </c>
-      <c r="I15" t="n">
-        <v>709</v>
-      </c>
-      <c r="J15" t="n">
-        <v>692</v>
-      </c>
-      <c r="K15" t="n">
-        <v>715</v>
-      </c>
       <c r="L15" t="n">
-        <v>672</v>
+        <v>658.8</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>582</v>
+        <v>648</v>
       </c>
       <c r="C16" t="n">
-        <v>587</v>
+        <v>626</v>
       </c>
       <c r="D16" t="n">
-        <v>659</v>
+        <v>577</v>
       </c>
       <c r="E16" t="n">
-        <v>755</v>
+        <v>669</v>
       </c>
       <c r="F16" t="n">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="G16" t="n">
+        <v>685</v>
+      </c>
+      <c r="H16" t="n">
+        <v>630</v>
+      </c>
+      <c r="I16" t="n">
+        <v>586</v>
+      </c>
+      <c r="J16" t="n">
         <v>676</v>
       </c>
-      <c r="H16" t="n">
-        <v>642</v>
-      </c>
-      <c r="I16" t="n">
-        <v>704</v>
-      </c>
-      <c r="J16" t="n">
-        <v>602</v>
-      </c>
       <c r="K16" t="n">
-        <v>661</v>
+        <v>588</v>
       </c>
       <c r="L16" t="n">
-        <v>652</v>
+        <v>635.2</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="C17" t="n">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="D17" t="n">
-        <v>652</v>
+        <v>611</v>
       </c>
       <c r="E17" t="n">
-        <v>711</v>
+        <v>570</v>
       </c>
       <c r="F17" t="n">
-        <v>548</v>
+        <v>692</v>
       </c>
       <c r="G17" t="n">
-        <v>678</v>
+        <v>569</v>
       </c>
       <c r="H17" t="n">
-        <v>597</v>
+        <v>668</v>
       </c>
       <c r="I17" t="n">
-        <v>607</v>
+        <v>714</v>
       </c>
       <c r="J17" t="n">
-        <v>584</v>
+        <v>660</v>
       </c>
       <c r="K17" t="n">
-        <v>610</v>
+        <v>639</v>
       </c>
       <c r="L17" t="n">
-        <v>627.3</v>
+        <v>641</v>
       </c>
     </row>
     <row r="18">
@@ -1082,34 +1082,34 @@
         <v>659</v>
       </c>
       <c r="C18" t="n">
-        <v>604</v>
+        <v>750</v>
       </c>
       <c r="D18" t="n">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E18" t="n">
-        <v>629</v>
+        <v>663</v>
       </c>
       <c r="F18" t="n">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="G18" t="n">
-        <v>639</v>
+        <v>671</v>
       </c>
       <c r="H18" t="n">
-        <v>665</v>
+        <v>745</v>
       </c>
       <c r="I18" t="n">
-        <v>759</v>
+        <v>737</v>
       </c>
       <c r="J18" t="n">
-        <v>672</v>
+        <v>821</v>
       </c>
       <c r="K18" t="n">
-        <v>653</v>
+        <v>708</v>
       </c>
       <c r="L18" t="n">
-        <v>663.4</v>
+        <v>709.2</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>583</v>
+        <v>712</v>
       </c>
       <c r="C19" t="n">
-        <v>620</v>
+        <v>713</v>
       </c>
       <c r="D19" t="n">
-        <v>595</v>
+        <v>683</v>
       </c>
       <c r="E19" t="n">
-        <v>747</v>
+        <v>644</v>
       </c>
       <c r="F19" t="n">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="G19" t="n">
-        <v>715</v>
+        <v>743</v>
       </c>
       <c r="H19" t="n">
-        <v>666</v>
+        <v>704</v>
       </c>
       <c r="I19" t="n">
-        <v>630</v>
+        <v>608</v>
       </c>
       <c r="J19" t="n">
-        <v>713</v>
+        <v>658</v>
       </c>
       <c r="K19" t="n">
-        <v>625</v>
+        <v>605</v>
       </c>
       <c r="L19" t="n">
-        <v>655.9</v>
+        <v>671.7</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>709</v>
+        <v>828</v>
       </c>
       <c r="C20" t="n">
-        <v>697</v>
+        <v>723</v>
       </c>
       <c r="D20" t="n">
-        <v>798</v>
+        <v>832</v>
       </c>
       <c r="E20" t="n">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="F20" t="n">
+        <v>595</v>
+      </c>
+      <c r="G20" t="n">
+        <v>703</v>
+      </c>
+      <c r="H20" t="n">
+        <v>852</v>
+      </c>
+      <c r="I20" t="n">
+        <v>707</v>
+      </c>
+      <c r="J20" t="n">
+        <v>666</v>
+      </c>
+      <c r="K20" t="n">
         <v>692</v>
       </c>
-      <c r="G20" t="n">
-        <v>749</v>
-      </c>
-      <c r="H20" t="n">
-        <v>740</v>
-      </c>
-      <c r="I20" t="n">
-        <v>746</v>
-      </c>
-      <c r="J20" t="n">
-        <v>685</v>
-      </c>
-      <c r="K20" t="n">
-        <v>775</v>
-      </c>
       <c r="L20" t="n">
-        <v>740.2</v>
+        <v>740.6</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>735</v>
+        <v>622</v>
       </c>
       <c r="C21" t="n">
-        <v>686</v>
+        <v>619</v>
       </c>
       <c r="D21" t="n">
-        <v>678</v>
+        <v>726</v>
       </c>
       <c r="E21" t="n">
-        <v>728</v>
+        <v>621</v>
       </c>
       <c r="F21" t="n">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="G21" t="n">
-        <v>720</v>
+        <v>637</v>
       </c>
       <c r="H21" t="n">
-        <v>633</v>
+        <v>784</v>
       </c>
       <c r="I21" t="n">
-        <v>637</v>
+        <v>580</v>
       </c>
       <c r="J21" t="n">
-        <v>614</v>
+        <v>731</v>
       </c>
       <c r="K21" t="n">
-        <v>607</v>
+        <v>549</v>
       </c>
       <c r="L21" t="n">
-        <v>669.9</v>
+        <v>651.8</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>589</v>
+        <v>620</v>
       </c>
       <c r="C22" t="n">
-        <v>602</v>
+        <v>570</v>
       </c>
       <c r="D22" t="n">
-        <v>621</v>
+        <v>701</v>
       </c>
       <c r="E22" t="n">
-        <v>573</v>
+        <v>610</v>
       </c>
       <c r="F22" t="n">
-        <v>651</v>
+        <v>568</v>
       </c>
       <c r="G22" t="n">
-        <v>557</v>
+        <v>669</v>
       </c>
       <c r="H22" t="n">
-        <v>571</v>
+        <v>626</v>
       </c>
       <c r="I22" t="n">
-        <v>593</v>
+        <v>532</v>
       </c>
       <c r="J22" t="n">
-        <v>576</v>
+        <v>617</v>
       </c>
       <c r="K22" t="n">
-        <v>578</v>
+        <v>625</v>
       </c>
       <c r="L22" t="n">
-        <v>591.1</v>
+        <v>613.8</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>539</v>
+        <v>640</v>
       </c>
       <c r="C23" t="n">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="D23" t="n">
-        <v>650</v>
+        <v>592</v>
       </c>
       <c r="E23" t="n">
+        <v>513</v>
+      </c>
+      <c r="F23" t="n">
         <v>592</v>
       </c>
-      <c r="F23" t="n">
-        <v>664</v>
-      </c>
       <c r="G23" t="n">
-        <v>557</v>
+        <v>700</v>
       </c>
       <c r="H23" t="n">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="I23" t="n">
-        <v>717</v>
+        <v>596</v>
       </c>
       <c r="J23" t="n">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="K23" t="n">
-        <v>663</v>
+        <v>631</v>
       </c>
       <c r="L23" t="n">
-        <v>620.4</v>
+        <v>615.4</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>688</v>
+        <v>583</v>
       </c>
       <c r="C24" t="n">
-        <v>667</v>
+        <v>642</v>
       </c>
       <c r="D24" t="n">
-        <v>635</v>
+        <v>655</v>
       </c>
       <c r="E24" t="n">
-        <v>664</v>
+        <v>646</v>
       </c>
       <c r="F24" t="n">
-        <v>686</v>
+        <v>651</v>
       </c>
       <c r="G24" t="n">
-        <v>685</v>
+        <v>641</v>
       </c>
       <c r="H24" t="n">
-        <v>657</v>
+        <v>621</v>
       </c>
       <c r="I24" t="n">
-        <v>604</v>
+        <v>655</v>
       </c>
       <c r="J24" t="n">
-        <v>715</v>
+        <v>692</v>
       </c>
       <c r="K24" t="n">
-        <v>654</v>
+        <v>700</v>
       </c>
       <c r="L24" t="n">
-        <v>665.5</v>
+        <v>648.6</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>749</v>
+        <v>639</v>
       </c>
       <c r="C25" t="n">
-        <v>644</v>
+        <v>584</v>
       </c>
       <c r="D25" t="n">
-        <v>741</v>
+        <v>636</v>
       </c>
       <c r="E25" t="n">
-        <v>648</v>
+        <v>567</v>
       </c>
       <c r="F25" t="n">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="G25" t="n">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="H25" t="n">
-        <v>656</v>
+        <v>732</v>
       </c>
       <c r="I25" t="n">
+        <v>686</v>
+      </c>
+      <c r="J25" t="n">
+        <v>609</v>
+      </c>
+      <c r="K25" t="n">
         <v>660</v>
       </c>
-      <c r="J25" t="n">
-        <v>722</v>
-      </c>
-      <c r="K25" t="n">
-        <v>685</v>
-      </c>
       <c r="L25" t="n">
-        <v>682</v>
+        <v>643.1</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>733</v>
+        <v>649</v>
       </c>
       <c r="C26" t="n">
-        <v>646</v>
+        <v>665</v>
       </c>
       <c r="D26" t="n">
-        <v>653</v>
+        <v>571</v>
       </c>
       <c r="E26" t="n">
-        <v>691</v>
+        <v>611</v>
       </c>
       <c r="F26" t="n">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="G26" t="n">
-        <v>608</v>
+        <v>719</v>
       </c>
       <c r="H26" t="n">
-        <v>681</v>
+        <v>595</v>
       </c>
       <c r="I26" t="n">
-        <v>772</v>
+        <v>722</v>
       </c>
       <c r="J26" t="n">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="K26" t="n">
-        <v>629</v>
+        <v>744</v>
       </c>
       <c r="L26" t="n">
-        <v>663.8</v>
+        <v>652.6</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>562</v>
+        <v>518</v>
       </c>
       <c r="C27" t="n">
-        <v>561</v>
+        <v>504</v>
       </c>
       <c r="D27" t="n">
-        <v>700</v>
+        <v>576</v>
       </c>
       <c r="E27" t="n">
-        <v>619</v>
+        <v>553</v>
       </c>
       <c r="F27" t="n">
-        <v>702</v>
+        <v>533</v>
       </c>
       <c r="G27" t="n">
-        <v>565</v>
+        <v>654</v>
       </c>
       <c r="H27" t="n">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="I27" t="n">
-        <v>591</v>
+        <v>554</v>
       </c>
       <c r="J27" t="n">
-        <v>507</v>
+        <v>633</v>
       </c>
       <c r="K27" t="n">
-        <v>630</v>
+        <v>685</v>
       </c>
       <c r="L27" t="n">
-        <v>604.4</v>
+        <v>579.7</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>680</v>
+        <v>561</v>
       </c>
       <c r="C28" t="n">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D28" t="n">
-        <v>600</v>
+        <v>746</v>
       </c>
       <c r="E28" t="n">
-        <v>696</v>
+        <v>635</v>
       </c>
       <c r="F28" t="n">
-        <v>798</v>
+        <v>721</v>
       </c>
       <c r="G28" t="n">
-        <v>636</v>
+        <v>752</v>
       </c>
       <c r="H28" t="n">
-        <v>605</v>
+        <v>654</v>
       </c>
       <c r="I28" t="n">
-        <v>662</v>
+        <v>720</v>
       </c>
       <c r="J28" t="n">
-        <v>669</v>
+        <v>871</v>
       </c>
       <c r="K28" t="n">
-        <v>757</v>
+        <v>634</v>
       </c>
       <c r="L28" t="n">
-        <v>676.7</v>
+        <v>695.6</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>594</v>
+        <v>646</v>
       </c>
       <c r="C29" t="n">
-        <v>659</v>
+        <v>624</v>
       </c>
       <c r="D29" t="n">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="E29" t="n">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="F29" t="n">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="G29" t="n">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="H29" t="n">
-        <v>635</v>
+        <v>674</v>
       </c>
       <c r="I29" t="n">
-        <v>570</v>
+        <v>682</v>
       </c>
       <c r="J29" t="n">
-        <v>620</v>
+        <v>758</v>
       </c>
       <c r="K29" t="n">
-        <v>633</v>
+        <v>602</v>
       </c>
       <c r="L29" t="n">
-        <v>629.3</v>
+        <v>657.2</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>676</v>
+        <v>689</v>
       </c>
       <c r="C30" t="n">
-        <v>702</v>
+        <v>609</v>
       </c>
       <c r="D30" t="n">
-        <v>681</v>
+        <v>644</v>
       </c>
       <c r="E30" t="n">
-        <v>646</v>
+        <v>627</v>
       </c>
       <c r="F30" t="n">
-        <v>661</v>
+        <v>617</v>
       </c>
       <c r="G30" t="n">
-        <v>651</v>
+        <v>620</v>
       </c>
       <c r="H30" t="n">
-        <v>593</v>
+        <v>645</v>
       </c>
       <c r="I30" t="n">
-        <v>637</v>
+        <v>667</v>
       </c>
       <c r="J30" t="n">
-        <v>582</v>
+        <v>664</v>
       </c>
       <c r="K30" t="n">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="L30" t="n">
-        <v>642.8</v>
+        <v>637.9</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>617</v>
+        <v>643</v>
       </c>
       <c r="C31" t="n">
+        <v>695</v>
+      </c>
+      <c r="D31" t="n">
+        <v>720</v>
+      </c>
+      <c r="E31" t="n">
+        <v>732</v>
+      </c>
+      <c r="F31" t="n">
+        <v>645</v>
+      </c>
+      <c r="G31" t="n">
         <v>727</v>
       </c>
-      <c r="D31" t="n">
-        <v>711</v>
-      </c>
-      <c r="E31" t="n">
-        <v>738</v>
-      </c>
-      <c r="F31" t="n">
-        <v>838</v>
-      </c>
-      <c r="G31" t="n">
-        <v>752</v>
-      </c>
       <c r="H31" t="n">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="I31" t="n">
-        <v>662</v>
+        <v>705</v>
       </c>
       <c r="J31" t="n">
-        <v>745</v>
+        <v>671</v>
       </c>
       <c r="K31" t="n">
-        <v>704</v>
+        <v>723</v>
       </c>
       <c r="L31" t="n">
-        <v>724.8</v>
+        <v>700.3</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>655</v>
+        <v>636</v>
       </c>
       <c r="C32" t="n">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D32" t="n">
-        <v>728</v>
+        <v>627</v>
       </c>
       <c r="E32" t="n">
-        <v>629</v>
+        <v>652</v>
       </c>
       <c r="F32" t="n">
-        <v>693</v>
+        <v>723</v>
       </c>
       <c r="G32" t="n">
-        <v>697</v>
+        <v>678</v>
       </c>
       <c r="H32" t="n">
-        <v>704</v>
+        <v>767</v>
       </c>
       <c r="I32" t="n">
-        <v>632</v>
+        <v>650</v>
       </c>
       <c r="J32" t="n">
-        <v>700</v>
+        <v>667</v>
       </c>
       <c r="K32" t="n">
-        <v>740</v>
+        <v>644</v>
       </c>
       <c r="L32" t="n">
-        <v>684.3</v>
+        <v>670.5</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>657</v>
+        <v>695</v>
       </c>
       <c r="C33" t="n">
-        <v>708</v>
+        <v>669</v>
       </c>
       <c r="D33" t="n">
-        <v>598</v>
+        <v>627</v>
       </c>
       <c r="E33" t="n">
-        <v>704</v>
+        <v>682</v>
       </c>
       <c r="F33" t="n">
-        <v>889</v>
+        <v>703</v>
       </c>
       <c r="G33" t="n">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="H33" t="n">
-        <v>643</v>
+        <v>688</v>
       </c>
       <c r="I33" t="n">
-        <v>766</v>
+        <v>663</v>
       </c>
       <c r="J33" t="n">
-        <v>686</v>
+        <v>862</v>
       </c>
       <c r="K33" t="n">
-        <v>794</v>
+        <v>720</v>
       </c>
       <c r="L33" t="n">
-        <v>717</v>
+        <v>703</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>635</v>
+        <v>650</v>
       </c>
       <c r="C34" t="n">
-        <v>588</v>
+        <v>638</v>
       </c>
       <c r="D34" t="n">
-        <v>715</v>
+        <v>734</v>
       </c>
       <c r="E34" t="n">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="F34" t="n">
-        <v>572</v>
+        <v>627</v>
       </c>
       <c r="G34" t="n">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="H34" t="n">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="I34" t="n">
-        <v>726</v>
+        <v>681</v>
       </c>
       <c r="J34" t="n">
-        <v>674</v>
+        <v>605</v>
       </c>
       <c r="K34" t="n">
-        <v>690</v>
+        <v>614</v>
       </c>
       <c r="L34" t="n">
-        <v>639.4</v>
+        <v>636.3</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>535</v>
+        <v>611</v>
       </c>
       <c r="C35" t="n">
-        <v>547</v>
+        <v>566</v>
       </c>
       <c r="D35" t="n">
+        <v>530</v>
+      </c>
+      <c r="E35" t="n">
+        <v>553</v>
+      </c>
+      <c r="F35" t="n">
         <v>555</v>
       </c>
-      <c r="E35" t="n">
-        <v>560</v>
-      </c>
-      <c r="F35" t="n">
-        <v>542</v>
-      </c>
       <c r="G35" t="n">
-        <v>597</v>
+        <v>727</v>
       </c>
       <c r="H35" t="n">
-        <v>536</v>
+        <v>591</v>
       </c>
       <c r="I35" t="n">
-        <v>566</v>
+        <v>543</v>
       </c>
       <c r="J35" t="n">
-        <v>620</v>
+        <v>692</v>
       </c>
       <c r="K35" t="n">
-        <v>585</v>
+        <v>716</v>
       </c>
       <c r="L35" t="n">
-        <v>564.3</v>
+        <v>608.4</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>679</v>
+        <v>653</v>
       </c>
       <c r="C36" t="n">
+        <v>658</v>
+      </c>
+      <c r="D36" t="n">
+        <v>733</v>
+      </c>
+      <c r="E36" t="n">
+        <v>659</v>
+      </c>
+      <c r="F36" t="n">
+        <v>717</v>
+      </c>
+      <c r="G36" t="n">
+        <v>694</v>
+      </c>
+      <c r="H36" t="n">
+        <v>584</v>
+      </c>
+      <c r="I36" t="n">
+        <v>684</v>
+      </c>
+      <c r="J36" t="n">
         <v>699</v>
       </c>
-      <c r="D36" t="n">
-        <v>643</v>
-      </c>
-      <c r="E36" t="n">
-        <v>673</v>
-      </c>
-      <c r="F36" t="n">
-        <v>732</v>
-      </c>
-      <c r="G36" t="n">
-        <v>681</v>
-      </c>
-      <c r="H36" t="n">
-        <v>647</v>
-      </c>
-      <c r="I36" t="n">
-        <v>669</v>
-      </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>700</v>
       </c>
-      <c r="K36" t="n">
-        <v>656</v>
-      </c>
       <c r="L36" t="n">
-        <v>677.9</v>
+        <v>678.1</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>620</v>
+        <v>593</v>
       </c>
       <c r="C37" t="n">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="D37" t="n">
-        <v>746</v>
+        <v>627</v>
       </c>
       <c r="E37" t="n">
-        <v>721</v>
+        <v>735</v>
       </c>
       <c r="F37" t="n">
-        <v>555</v>
+        <v>708</v>
       </c>
       <c r="G37" t="n">
-        <v>648</v>
+        <v>772</v>
       </c>
       <c r="H37" t="n">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="I37" t="n">
-        <v>593</v>
+        <v>661</v>
       </c>
       <c r="J37" t="n">
-        <v>686</v>
+        <v>818</v>
       </c>
       <c r="K37" t="n">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="L37" t="n">
-        <v>659</v>
+        <v>692.8</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>692</v>
+        <v>608</v>
       </c>
       <c r="C38" t="n">
-        <v>677</v>
+        <v>581</v>
       </c>
       <c r="D38" t="n">
-        <v>664</v>
+        <v>577</v>
       </c>
       <c r="E38" t="n">
-        <v>601</v>
+        <v>620</v>
       </c>
       <c r="F38" t="n">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="G38" t="n">
-        <v>561</v>
+        <v>651</v>
       </c>
       <c r="H38" t="n">
-        <v>621</v>
+        <v>712</v>
       </c>
       <c r="I38" t="n">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="J38" t="n">
-        <v>654</v>
+        <v>620</v>
       </c>
       <c r="K38" t="n">
-        <v>719</v>
+        <v>517</v>
       </c>
       <c r="L38" t="n">
-        <v>637.2</v>
+        <v>603.6</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>539</v>
+        <v>561</v>
       </c>
       <c r="C39" t="n">
-        <v>648</v>
+        <v>552</v>
       </c>
       <c r="D39" t="n">
-        <v>577</v>
+        <v>538</v>
       </c>
       <c r="E39" t="n">
-        <v>557</v>
+        <v>521</v>
       </c>
       <c r="F39" t="n">
-        <v>594</v>
+        <v>500</v>
       </c>
       <c r="G39" t="n">
-        <v>578</v>
+        <v>548</v>
       </c>
       <c r="H39" t="n">
-        <v>583</v>
+        <v>525</v>
       </c>
       <c r="I39" t="n">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="J39" t="n">
-        <v>580</v>
+        <v>524</v>
       </c>
       <c r="K39" t="n">
-        <v>554</v>
+        <v>574</v>
       </c>
       <c r="L39" t="n">
-        <v>580.8</v>
+        <v>543</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="C40" t="n">
-        <v>698</v>
+        <v>614</v>
       </c>
       <c r="D40" t="n">
-        <v>572</v>
+        <v>666</v>
       </c>
       <c r="E40" t="n">
-        <v>645</v>
+        <v>593</v>
       </c>
       <c r="F40" t="n">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="G40" t="n">
-        <v>602</v>
+        <v>684</v>
       </c>
       <c r="H40" t="n">
-        <v>695</v>
+        <v>593</v>
       </c>
       <c r="I40" t="n">
-        <v>711</v>
+        <v>651</v>
       </c>
       <c r="J40" t="n">
-        <v>605</v>
+        <v>582</v>
       </c>
       <c r="K40" t="n">
-        <v>648</v>
+        <v>625</v>
       </c>
       <c r="L40" t="n">
-        <v>643.8</v>
+        <v>628.3</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
+        <v>602</v>
+      </c>
+      <c r="C41" t="n">
+        <v>560</v>
+      </c>
+      <c r="D41" t="n">
+        <v>730</v>
+      </c>
+      <c r="E41" t="n">
+        <v>597</v>
+      </c>
+      <c r="F41" t="n">
+        <v>639</v>
+      </c>
+      <c r="G41" t="n">
+        <v>634</v>
+      </c>
+      <c r="H41" t="n">
         <v>652</v>
-      </c>
-      <c r="C41" t="n">
-        <v>686</v>
-      </c>
-      <c r="D41" t="n">
-        <v>618</v>
-      </c>
-      <c r="E41" t="n">
-        <v>590</v>
-      </c>
-      <c r="F41" t="n">
-        <v>774</v>
-      </c>
-      <c r="G41" t="n">
-        <v>578</v>
-      </c>
-      <c r="H41" t="n">
-        <v>664</v>
       </c>
       <c r="I41" t="n">
         <v>623</v>
       </c>
       <c r="J41" t="n">
-        <v>620</v>
+        <v>655</v>
       </c>
       <c r="K41" t="n">
-        <v>641</v>
+        <v>610</v>
       </c>
       <c r="L41" t="n">
-        <v>644.6</v>
+        <v>630.2</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>607</v>
+        <v>686</v>
       </c>
       <c r="C42" t="n">
-        <v>640</v>
+        <v>559</v>
       </c>
       <c r="D42" t="n">
-        <v>594</v>
+        <v>662</v>
       </c>
       <c r="E42" t="n">
-        <v>584</v>
+        <v>713</v>
       </c>
       <c r="F42" t="n">
-        <v>689</v>
+        <v>638</v>
       </c>
       <c r="G42" t="n">
-        <v>600</v>
+        <v>636</v>
       </c>
       <c r="H42" t="n">
-        <v>712</v>
+        <v>647</v>
       </c>
       <c r="I42" t="n">
-        <v>669</v>
+        <v>719</v>
       </c>
       <c r="J42" t="n">
-        <v>552</v>
+        <v>697</v>
       </c>
       <c r="K42" t="n">
-        <v>613</v>
+        <v>641</v>
       </c>
       <c r="L42" t="n">
-        <v>626</v>
+        <v>659.8</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>772</v>
+        <v>708</v>
       </c>
       <c r="C43" t="n">
-        <v>770</v>
+        <v>681</v>
       </c>
       <c r="D43" t="n">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="E43" t="n">
-        <v>733</v>
+        <v>624</v>
       </c>
       <c r="F43" t="n">
-        <v>641</v>
+        <v>788</v>
       </c>
       <c r="G43" t="n">
-        <v>734</v>
+        <v>766</v>
       </c>
       <c r="H43" t="n">
-        <v>672</v>
+        <v>702</v>
       </c>
       <c r="I43" t="n">
-        <v>832</v>
+        <v>716</v>
       </c>
       <c r="J43" t="n">
-        <v>735</v>
+        <v>622</v>
       </c>
       <c r="K43" t="n">
-        <v>628</v>
+        <v>695</v>
       </c>
       <c r="L43" t="n">
-        <v>725.6</v>
+        <v>704.3</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>572</v>
+        <v>632</v>
       </c>
       <c r="C44" t="n">
-        <v>671</v>
+        <v>703</v>
       </c>
       <c r="D44" t="n">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="E44" t="n">
-        <v>528</v>
+        <v>629</v>
       </c>
       <c r="F44" t="n">
-        <v>616</v>
+        <v>719</v>
       </c>
       <c r="G44" t="n">
-        <v>523</v>
+        <v>637</v>
       </c>
       <c r="H44" t="n">
-        <v>592</v>
+        <v>690</v>
       </c>
       <c r="I44" t="n">
-        <v>654</v>
+        <v>546</v>
       </c>
       <c r="J44" t="n">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="K44" t="n">
-        <v>660</v>
+        <v>557</v>
       </c>
       <c r="L44" t="n">
-        <v>598.4</v>
+        <v>630.5</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>702</v>
+        <v>663</v>
       </c>
       <c r="C45" t="n">
+        <v>724</v>
+      </c>
+      <c r="D45" t="n">
+        <v>637</v>
+      </c>
+      <c r="E45" t="n">
+        <v>770</v>
+      </c>
+      <c r="F45" t="n">
+        <v>654</v>
+      </c>
+      <c r="G45" t="n">
+        <v>592</v>
+      </c>
+      <c r="H45" t="n">
         <v>717</v>
       </c>
-      <c r="D45" t="n">
-        <v>620</v>
-      </c>
-      <c r="E45" t="n">
-        <v>696</v>
-      </c>
-      <c r="F45" t="n">
-        <v>659</v>
-      </c>
-      <c r="G45" t="n">
-        <v>669</v>
-      </c>
-      <c r="H45" t="n">
-        <v>602</v>
-      </c>
       <c r="I45" t="n">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="J45" t="n">
-        <v>599</v>
+        <v>645</v>
       </c>
       <c r="K45" t="n">
         <v>644</v>
       </c>
       <c r="L45" t="n">
-        <v>659.7</v>
+        <v>670.9</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="C46" t="n">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="D46" t="n">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="E46" t="n">
-        <v>608</v>
+        <v>666</v>
       </c>
       <c r="F46" t="n">
-        <v>599</v>
+        <v>571</v>
       </c>
       <c r="G46" t="n">
-        <v>641</v>
+        <v>713</v>
       </c>
       <c r="H46" t="n">
-        <v>672</v>
+        <v>698</v>
       </c>
       <c r="I46" t="n">
-        <v>596</v>
+        <v>656</v>
       </c>
       <c r="J46" t="n">
-        <v>683</v>
+        <v>579</v>
       </c>
       <c r="K46" t="n">
-        <v>642</v>
+        <v>576</v>
       </c>
       <c r="L46" t="n">
-        <v>632.8</v>
+        <v>639.9</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>632</v>
+        <v>552</v>
       </c>
       <c r="C47" t="n">
-        <v>641</v>
+        <v>798</v>
       </c>
       <c r="D47" t="n">
-        <v>530</v>
+        <v>591</v>
       </c>
       <c r="E47" t="n">
-        <v>634</v>
+        <v>701</v>
       </c>
       <c r="F47" t="n">
-        <v>628</v>
+        <v>649</v>
       </c>
       <c r="G47" t="n">
-        <v>603</v>
+        <v>580</v>
       </c>
       <c r="H47" t="n">
-        <v>559</v>
+        <v>652</v>
       </c>
       <c r="I47" t="n">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="J47" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K47" t="n">
-        <v>573</v>
+        <v>631</v>
       </c>
       <c r="L47" t="n">
-        <v>598.1</v>
+        <v>631.9</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="C48" t="n">
-        <v>756</v>
+        <v>683</v>
       </c>
       <c r="D48" t="n">
-        <v>763</v>
+        <v>691</v>
       </c>
       <c r="E48" t="n">
-        <v>720</v>
+        <v>703</v>
       </c>
       <c r="F48" t="n">
-        <v>706</v>
+        <v>736</v>
       </c>
       <c r="G48" t="n">
-        <v>714</v>
+        <v>667</v>
       </c>
       <c r="H48" t="n">
-        <v>701</v>
+        <v>715</v>
       </c>
       <c r="I48" t="n">
-        <v>721</v>
+        <v>702</v>
       </c>
       <c r="J48" t="n">
-        <v>834</v>
+        <v>730</v>
       </c>
       <c r="K48" t="n">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="L48" t="n">
-        <v>735.8</v>
+        <v>705</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>778</v>
+        <v>732</v>
       </c>
       <c r="C49" t="n">
-        <v>659</v>
+        <v>677</v>
       </c>
       <c r="D49" t="n">
-        <v>760</v>
+        <v>656</v>
       </c>
       <c r="E49" t="n">
-        <v>804</v>
+        <v>702</v>
       </c>
       <c r="F49" t="n">
-        <v>812</v>
+        <v>766</v>
       </c>
       <c r="G49" t="n">
-        <v>598</v>
+        <v>792</v>
       </c>
       <c r="H49" t="n">
-        <v>744</v>
+        <v>676</v>
       </c>
       <c r="I49" t="n">
-        <v>717</v>
+        <v>628</v>
       </c>
       <c r="J49" t="n">
-        <v>660</v>
+        <v>625</v>
       </c>
       <c r="K49" t="n">
-        <v>747</v>
+        <v>757</v>
       </c>
       <c r="L49" t="n">
-        <v>727.9</v>
+        <v>701.1</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>700</v>
+        <v>639</v>
       </c>
       <c r="C50" t="n">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D50" t="n">
-        <v>749</v>
+        <v>582</v>
       </c>
       <c r="E50" t="n">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="F50" t="n">
-        <v>611</v>
+        <v>694</v>
       </c>
       <c r="G50" t="n">
+        <v>615</v>
+      </c>
+      <c r="H50" t="n">
+        <v>696</v>
+      </c>
+      <c r="I50" t="n">
+        <v>639</v>
+      </c>
+      <c r="J50" t="n">
         <v>656</v>
       </c>
-      <c r="H50" t="n">
-        <v>660</v>
-      </c>
-      <c r="I50" t="n">
-        <v>615</v>
-      </c>
-      <c r="J50" t="n">
-        <v>731</v>
-      </c>
       <c r="K50" t="n">
-        <v>634</v>
+        <v>710</v>
       </c>
       <c r="L50" t="n">
-        <v>663.4</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
+        <v>696</v>
+      </c>
+      <c r="C51" t="n">
+        <v>699</v>
+      </c>
+      <c r="D51" t="n">
+        <v>701</v>
+      </c>
+      <c r="E51" t="n">
+        <v>645</v>
+      </c>
+      <c r="F51" t="n">
+        <v>821</v>
+      </c>
+      <c r="G51" t="n">
+        <v>737</v>
+      </c>
+      <c r="H51" t="n">
+        <v>693</v>
+      </c>
+      <c r="I51" t="n">
         <v>644</v>
       </c>
-      <c r="C51" t="n">
-        <v>614</v>
-      </c>
-      <c r="D51" t="n">
-        <v>620</v>
-      </c>
-      <c r="E51" t="n">
-        <v>656</v>
-      </c>
-      <c r="F51" t="n">
-        <v>732</v>
-      </c>
-      <c r="G51" t="n">
-        <v>736</v>
-      </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>648</v>
       </c>
-      <c r="I51" t="n">
-        <v>755</v>
-      </c>
-      <c r="J51" t="n">
-        <v>639</v>
-      </c>
       <c r="K51" t="n">
-        <v>572</v>
+        <v>721</v>
       </c>
       <c r="L51" t="n">
-        <v>661.6</v>
+        <v>700.5</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>646.0599999999999</v>
+        <v>646.14</v>
       </c>
       <c r="C52" t="n">
-        <v>652</v>
+        <v>646.52</v>
       </c>
       <c r="D52" t="n">
-        <v>644.22</v>
+        <v>639.48</v>
       </c>
       <c r="E52" t="n">
-        <v>653.08</v>
+        <v>644.12</v>
       </c>
       <c r="F52" t="n">
-        <v>654.6799999999999</v>
+        <v>646.72</v>
       </c>
       <c r="G52" t="n">
-        <v>644.08</v>
+        <v>664.16</v>
       </c>
       <c r="H52" t="n">
-        <v>643.62</v>
+        <v>667.58</v>
       </c>
       <c r="I52" t="n">
-        <v>655.34</v>
+        <v>641.72</v>
       </c>
       <c r="J52" t="n">
-        <v>643.26</v>
+        <v>655.46</v>
       </c>
       <c r="K52" t="n">
-        <v>653.86</v>
+        <v>644.96</v>
       </c>
       <c r="L52" t="n">
-        <v>649.02</v>
+        <v>649.686</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5.172852993011475</v>
+        <v>4.865842580795288</v>
       </c>
       <c r="C2" t="n">
-        <v>4.013760328292847</v>
+        <v>3.861959457397461</v>
       </c>
       <c r="D2" t="n">
-        <v>4.112757205963135</v>
+        <v>4.166195392608643</v>
       </c>
       <c r="E2" t="n">
-        <v>3.959410429000854</v>
+        <v>4.669382095336914</v>
       </c>
       <c r="F2" t="n">
-        <v>4.033220767974854</v>
+        <v>4.049471139907837</v>
       </c>
       <c r="G2" t="n">
-        <v>4.12496018409729</v>
+        <v>3.961198091506958</v>
       </c>
       <c r="H2" t="n">
-        <v>4.351427316665649</v>
+        <v>4.555180311203003</v>
       </c>
       <c r="I2" t="n">
-        <v>4.299544095993042</v>
+        <v>4.206076860427856</v>
       </c>
       <c r="J2" t="n">
-        <v>4.22125506401062</v>
+        <v>3.862957000732422</v>
       </c>
       <c r="K2" t="n">
-        <v>4.072132349014282</v>
+        <v>4.230802059173584</v>
       </c>
       <c r="L2" t="n">
-        <v>4.236132073402405</v>
+        <v>4.242906498908996</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>5.001249313354492</v>
+        <v>4.362380981445312</v>
       </c>
       <c r="C3" t="n">
-        <v>4.411763191223145</v>
+        <v>4.962377071380615</v>
       </c>
       <c r="D3" t="n">
-        <v>4.932922840118408</v>
+        <v>4.877570152282715</v>
       </c>
       <c r="E3" t="n">
-        <v>4.510001420974731</v>
+        <v>4.663630485534668</v>
       </c>
       <c r="F3" t="n">
-        <v>4.657626628875732</v>
+        <v>5.409245729446411</v>
       </c>
       <c r="G3" t="n">
-        <v>4.271109342575073</v>
+        <v>4.172364711761475</v>
       </c>
       <c r="H3" t="n">
-        <v>4.156421661376953</v>
+        <v>6.7203688621521</v>
       </c>
       <c r="I3" t="n">
-        <v>4.537914752960205</v>
+        <v>4.39956259727478</v>
       </c>
       <c r="J3" t="n">
-        <v>4.482064247131348</v>
+        <v>4.504807472229004</v>
       </c>
       <c r="K3" t="n">
-        <v>4.436678409576416</v>
+        <v>4.272379159927368</v>
       </c>
       <c r="L3" t="n">
-        <v>4.53977518081665</v>
+        <v>4.834468722343445</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>3.864158630371094</v>
+        <v>3.592683553695679</v>
       </c>
       <c r="C4" t="n">
-        <v>3.773413181304932</v>
+        <v>3.845999002456665</v>
       </c>
       <c r="D4" t="n">
-        <v>4.215253353118896</v>
+        <v>3.821065425872803</v>
       </c>
       <c r="E4" t="n">
-        <v>4.741402864456177</v>
+        <v>4.0076003074646</v>
       </c>
       <c r="F4" t="n">
-        <v>3.958900690078735</v>
+        <v>4.578088998794556</v>
       </c>
       <c r="G4" t="n">
-        <v>3.557438373565674</v>
+        <v>3.858250379562378</v>
       </c>
       <c r="H4" t="n">
-        <v>4.33297061920166</v>
+        <v>3.908581495285034</v>
       </c>
       <c r="I4" t="n">
-        <v>3.723207473754883</v>
+        <v>3.6167893409729</v>
       </c>
       <c r="J4" t="n">
-        <v>3.863953351974487</v>
+        <v>3.708070993423462</v>
       </c>
       <c r="K4" t="n">
-        <v>3.776182413101196</v>
+        <v>3.627268075942993</v>
       </c>
       <c r="L4" t="n">
-        <v>3.980688095092773</v>
+        <v>3.856439757347107</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>4.327238321304321</v>
+        <v>4.096093654632568</v>
       </c>
       <c r="C5" t="n">
-        <v>3.913308382034302</v>
+        <v>4.355432510375977</v>
       </c>
       <c r="D5" t="n">
-        <v>4.126744985580444</v>
+        <v>4.315505981445312</v>
       </c>
       <c r="E5" t="n">
-        <v>3.835742235183716</v>
+        <v>3.742979526519775</v>
       </c>
       <c r="F5" t="n">
-        <v>3.848191261291504</v>
+        <v>4.320512294769287</v>
       </c>
       <c r="G5" t="n">
-        <v>4.23719334602356</v>
+        <v>4.104533433914185</v>
       </c>
       <c r="H5" t="n">
-        <v>4.234713554382324</v>
+        <v>4.127512693405151</v>
       </c>
       <c r="I5" t="n">
-        <v>4.123975038528442</v>
+        <v>3.808866024017334</v>
       </c>
       <c r="J5" t="n">
-        <v>4.22921895980835</v>
+        <v>3.774912595748901</v>
       </c>
       <c r="K5" t="n">
-        <v>3.833216905593872</v>
+        <v>3.968920230865479</v>
       </c>
       <c r="L5" t="n">
-        <v>4.070954298973083</v>
+        <v>4.061526894569397</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>4.140480279922485</v>
+        <v>3.935469627380371</v>
       </c>
       <c r="C6" t="n">
-        <v>4.239201784133911</v>
+        <v>4.088106155395508</v>
       </c>
       <c r="D6" t="n">
-        <v>4.276597499847412</v>
+        <v>4.125997543334961</v>
       </c>
       <c r="E6" t="n">
-        <v>4.078615188598633</v>
+        <v>4.132970809936523</v>
       </c>
       <c r="F6" t="n">
-        <v>4.071145296096802</v>
+        <v>3.981873989105225</v>
       </c>
       <c r="G6" t="n">
-        <v>3.811272859573364</v>
+        <v>4.240706443786621</v>
       </c>
       <c r="H6" t="n">
-        <v>4.134962797164917</v>
+        <v>4.447715044021606</v>
       </c>
       <c r="I6" t="n">
-        <v>4.199287414550781</v>
+        <v>4.12400221824646</v>
       </c>
       <c r="J6" t="n">
-        <v>3.997833728790283</v>
+        <v>4.0137939453125</v>
       </c>
       <c r="K6" t="n">
-        <v>4.851616382598877</v>
+        <v>4.100164175033569</v>
       </c>
       <c r="L6" t="n">
-        <v>4.180101323127746</v>
+        <v>4.119079995155334</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>3.946947574615479</v>
+        <v>3.655004024505615</v>
       </c>
       <c r="C7" t="n">
-        <v>3.676624774932861</v>
+        <v>3.936287403106689</v>
       </c>
       <c r="D7" t="n">
-        <v>4.402777910232544</v>
+        <v>3.978666543960571</v>
       </c>
       <c r="E7" t="n">
-        <v>3.851685762405396</v>
+        <v>4.328249454498291</v>
       </c>
       <c r="F7" t="n">
-        <v>4.062632083892822</v>
+        <v>4.067470550537109</v>
       </c>
       <c r="G7" t="n">
-        <v>4.148457050323486</v>
+        <v>3.858480453491211</v>
       </c>
       <c r="H7" t="n">
-        <v>3.98433518409729</v>
+        <v>4.683347702026367</v>
       </c>
       <c r="I7" t="n">
-        <v>3.990847110748291</v>
+        <v>3.798614978790283</v>
       </c>
       <c r="J7" t="n">
-        <v>3.905540227890015</v>
+        <v>3.949734926223755</v>
       </c>
       <c r="K7" t="n">
-        <v>3.909546136856079</v>
+        <v>3.844997882843018</v>
       </c>
       <c r="L7" t="n">
-        <v>3.987939381599426</v>
+        <v>4.010085391998291</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>3.919492483139038</v>
+        <v>4.399581909179688</v>
       </c>
       <c r="C8" t="n">
-        <v>4.593297481536865</v>
+        <v>4.14924430847168</v>
       </c>
       <c r="D8" t="n">
-        <v>3.997822284698486</v>
+        <v>4.281908988952637</v>
       </c>
       <c r="E8" t="n">
-        <v>4.288579702377319</v>
+        <v>4.291530132293701</v>
       </c>
       <c r="F8" t="n">
-        <v>4.111019134521484</v>
+        <v>4.010988712310791</v>
       </c>
       <c r="G8" t="n">
-        <v>3.931483030319214</v>
+        <v>3.870673418045044</v>
       </c>
       <c r="H8" t="n">
-        <v>4.188327550888062</v>
+        <v>3.796331882476807</v>
       </c>
       <c r="I8" t="n">
-        <v>4.272110223770142</v>
+        <v>4.786869764328003</v>
       </c>
       <c r="J8" t="n">
-        <v>3.847694873809814</v>
+        <v>4.264288425445557</v>
       </c>
       <c r="K8" t="n">
-        <v>3.939450263977051</v>
+        <v>4.353437423706055</v>
       </c>
       <c r="L8" t="n">
-        <v>4.108927702903747</v>
+        <v>4.220485496520996</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.701082229614258</v>
+        <v>3.529512882232666</v>
       </c>
       <c r="C9" t="n">
-        <v>3.710040807723999</v>
+        <v>3.664661407470703</v>
       </c>
       <c r="D9" t="n">
-        <v>3.706052303314209</v>
+        <v>3.599862813949585</v>
       </c>
       <c r="E9" t="n">
-        <v>3.698076486587524</v>
+        <v>3.606815576553345</v>
       </c>
       <c r="F9" t="n">
-        <v>3.787357807159424</v>
+        <v>3.481639623641968</v>
       </c>
       <c r="G9" t="n">
-        <v>3.925497531890869</v>
+        <v>3.576926469802856</v>
       </c>
       <c r="H9" t="n">
-        <v>4.01179027557373</v>
+        <v>4.199299812316895</v>
       </c>
       <c r="I9" t="n">
-        <v>3.575898885726929</v>
+        <v>3.725017309188843</v>
       </c>
       <c r="J9" t="n">
-        <v>3.858150005340576</v>
+        <v>3.501580715179443</v>
       </c>
       <c r="K9" t="n">
-        <v>3.951430797576904</v>
+        <v>3.981359958648682</v>
       </c>
       <c r="L9" t="n">
-        <v>3.792537713050842</v>
+        <v>3.686667656898499</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>4.709503412246704</v>
+        <v>5.182320117950439</v>
       </c>
       <c r="C10" t="n">
-        <v>4.680059432983398</v>
+        <v>4.803780317306519</v>
       </c>
       <c r="D10" t="n">
-        <v>4.943397760391235</v>
+        <v>4.782835960388184</v>
       </c>
       <c r="E10" t="n">
-        <v>5.22669506072998</v>
+        <v>4.875113487243652</v>
       </c>
       <c r="F10" t="n">
-        <v>5.407236576080322</v>
+        <v>5.055119752883911</v>
       </c>
       <c r="G10" t="n">
-        <v>4.950859308242798</v>
+        <v>4.933913707733154</v>
       </c>
       <c r="H10" t="n">
-        <v>5.075573921203613</v>
+        <v>5.011273622512817</v>
       </c>
       <c r="I10" t="n">
-        <v>4.717462778091431</v>
+        <v>4.807751893997192</v>
       </c>
       <c r="J10" t="n">
-        <v>5.056089162826538</v>
+        <v>4.811811923980713</v>
       </c>
       <c r="K10" t="n">
-        <v>5.13440990447998</v>
+        <v>5.220040082931519</v>
       </c>
       <c r="L10" t="n">
-        <v>4.9901287317276</v>
+        <v>4.94839608669281</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.281101226806641</v>
+        <v>4.456605195999146</v>
       </c>
       <c r="C11" t="n">
-        <v>5.130420684814453</v>
+        <v>4.699272871017456</v>
       </c>
       <c r="D11" t="n">
-        <v>5.500506639480591</v>
+        <v>4.190109968185425</v>
       </c>
       <c r="E11" t="n">
-        <v>4.486036062240601</v>
+        <v>4.347002744674683</v>
       </c>
       <c r="F11" t="n">
-        <v>4.260396480560303</v>
+        <v>4.481853246688843</v>
       </c>
       <c r="G11" t="n">
-        <v>4.268891096115112</v>
+        <v>4.755131483078003</v>
       </c>
       <c r="H11" t="n">
-        <v>4.991034984588623</v>
+        <v>4.616000413894653</v>
       </c>
       <c r="I11" t="n">
-        <v>4.401572227478027</v>
+        <v>4.18219518661499</v>
       </c>
       <c r="J11" t="n">
-        <v>4.8673255443573</v>
+        <v>5.045850276947021</v>
       </c>
       <c r="K11" t="n">
-        <v>4.462883710861206</v>
+        <v>5.56162166595459</v>
       </c>
       <c r="L11" t="n">
-        <v>4.665016865730285</v>
+        <v>4.633564305305481</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>3.964700222015381</v>
+        <v>4.189133405685425</v>
       </c>
       <c r="C12" t="n">
-        <v>4.047462701797485</v>
+        <v>4.344776391983032</v>
       </c>
       <c r="D12" t="n">
-        <v>3.941236972808838</v>
+        <v>3.815291404724121</v>
       </c>
       <c r="E12" t="n">
-        <v>4.17412281036377</v>
+        <v>3.863665342330933</v>
       </c>
       <c r="F12" t="n">
-        <v>3.841005802154541</v>
+        <v>3.968417406082153</v>
       </c>
       <c r="G12" t="n">
-        <v>4.159181833267212</v>
+        <v>4.137484550476074</v>
       </c>
       <c r="H12" t="n">
-        <v>4.36214804649353</v>
+        <v>4.287091255187988</v>
       </c>
       <c r="I12" t="n">
-        <v>4.025448560714722</v>
+        <v>3.997830867767334</v>
       </c>
       <c r="J12" t="n">
-        <v>3.77639365196228</v>
+        <v>3.718025684356689</v>
       </c>
       <c r="K12" t="n">
-        <v>4.096049547195435</v>
+        <v>4.090121746063232</v>
       </c>
       <c r="L12" t="n">
-        <v>4.038775014877319</v>
+        <v>4.041183805465698</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4.874092817306519</v>
+        <v>5.76034951210022</v>
       </c>
       <c r="C13" t="n">
-        <v>5.385779142379761</v>
+        <v>5.428190231323242</v>
       </c>
       <c r="D13" t="n">
-        <v>4.468117475509644</v>
+        <v>4.636180400848389</v>
       </c>
       <c r="E13" t="n">
-        <v>5.737893104553223</v>
+        <v>5.976848125457764</v>
       </c>
       <c r="F13" t="n">
-        <v>5.818160533905029</v>
+        <v>4.629196882247925</v>
       </c>
       <c r="G13" t="n">
-        <v>5.959812641143799</v>
+        <v>5.610764741897583</v>
       </c>
       <c r="H13" t="n">
-        <v>5.845088481903076</v>
+        <v>4.822854995727539</v>
       </c>
       <c r="I13" t="n">
-        <v>5.302987098693848</v>
+        <v>5.087287187576294</v>
       </c>
       <c r="J13" t="n">
-        <v>5.247622013092041</v>
+        <v>4.784561634063721</v>
       </c>
       <c r="K13" t="n">
-        <v>5.869518041610718</v>
+        <v>5.814204931259155</v>
       </c>
       <c r="L13" t="n">
-        <v>5.450907135009766</v>
+        <v>5.255043864250183</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.190322637557983</v>
+        <v>4.038704633712769</v>
       </c>
       <c r="C14" t="n">
-        <v>4.599271774291992</v>
+        <v>3.862687587738037</v>
       </c>
       <c r="D14" t="n">
-        <v>4.423725366592407</v>
+        <v>4.240195989608765</v>
       </c>
       <c r="E14" t="n">
-        <v>4.021730661392212</v>
+        <v>4.028736114501953</v>
       </c>
       <c r="F14" t="n">
-        <v>4.882082223892212</v>
+        <v>4.425736665725708</v>
       </c>
       <c r="G14" t="n">
-        <v>4.164878606796265</v>
+        <v>4.631737232208252</v>
       </c>
       <c r="H14" t="n">
-        <v>4.75290584564209</v>
+        <v>5.31061863899231</v>
       </c>
       <c r="I14" t="n">
-        <v>3.84418773651123</v>
+        <v>4.320566177368164</v>
       </c>
       <c r="J14" t="n">
-        <v>4.287551879882812</v>
+        <v>4.706561326980591</v>
       </c>
       <c r="K14" t="n">
-        <v>4.763355493545532</v>
+        <v>4.205310344696045</v>
       </c>
       <c r="L14" t="n">
-        <v>4.393001222610474</v>
+        <v>4.37708547115326</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.934927940368652</v>
+        <v>4.754928827285767</v>
       </c>
       <c r="C15" t="n">
-        <v>4.587292671203613</v>
+        <v>4.772346496582031</v>
       </c>
       <c r="D15" t="n">
-        <v>4.569384574890137</v>
+        <v>4.704520225524902</v>
       </c>
       <c r="E15" t="n">
-        <v>4.903526544570923</v>
+        <v>4.344971656799316</v>
       </c>
       <c r="F15" t="n">
-        <v>4.773852348327637</v>
+        <v>4.502043962478638</v>
       </c>
       <c r="G15" t="n">
-        <v>4.997270822525024</v>
+        <v>4.96786642074585</v>
       </c>
       <c r="H15" t="n">
-        <v>5.346851348876953</v>
+        <v>5.424194574356079</v>
       </c>
       <c r="I15" t="n">
-        <v>4.806768655776978</v>
+        <v>4.677515745162964</v>
       </c>
       <c r="J15" t="n">
-        <v>4.658633947372437</v>
+        <v>4.297327756881714</v>
       </c>
       <c r="K15" t="n">
-        <v>5.077051639556885</v>
+        <v>4.376120090484619</v>
       </c>
       <c r="L15" t="n">
-        <v>4.865556049346924</v>
+        <v>4.682183575630188</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.108922719955444</v>
+        <v>5.404971599578857</v>
       </c>
       <c r="C16" t="n">
-        <v>4.067925214767456</v>
+        <v>4.240971088409424</v>
       </c>
       <c r="D16" t="n">
-        <v>4.254641532897949</v>
+        <v>4.052453517913818</v>
       </c>
       <c r="E16" t="n">
-        <v>5.090528249740601</v>
+        <v>4.430989742279053</v>
       </c>
       <c r="F16" t="n">
-        <v>4.26764702796936</v>
+        <v>4.110405445098877</v>
       </c>
       <c r="G16" t="n">
-        <v>4.542903423309326</v>
+        <v>4.063648700714111</v>
       </c>
       <c r="H16" t="n">
-        <v>4.236209630966187</v>
+        <v>3.971901416778564</v>
       </c>
       <c r="I16" t="n">
-        <v>4.471123933792114</v>
+        <v>3.937485694885254</v>
       </c>
       <c r="J16" t="n">
-        <v>4.512007713317871</v>
+        <v>4.302533626556396</v>
       </c>
       <c r="K16" t="n">
-        <v>4.172365427017212</v>
+        <v>4.15395450592041</v>
       </c>
       <c r="L16" t="n">
-        <v>4.372427487373352</v>
+        <v>4.266931533813477</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.69706916809082</v>
+        <v>4.893531084060669</v>
       </c>
       <c r="C17" t="n">
-        <v>4.28359842300415</v>
+        <v>4.536469697952271</v>
       </c>
       <c r="D17" t="n">
-        <v>4.372847557067871</v>
+        <v>4.235204458236694</v>
       </c>
       <c r="E17" t="n">
-        <v>5.080039978027344</v>
+        <v>4.12103009223938</v>
       </c>
       <c r="F17" t="n">
-        <v>4.155406713485718</v>
+        <v>5.586503028869629</v>
       </c>
       <c r="G17" t="n">
-        <v>4.302526712417603</v>
+        <v>4.254942178726196</v>
       </c>
       <c r="H17" t="n">
-        <v>4.879072666168213</v>
+        <v>4.722255945205688</v>
       </c>
       <c r="I17" t="n">
-        <v>4.361369132995605</v>
+        <v>4.479860544204712</v>
       </c>
       <c r="J17" t="n">
-        <v>4.264633893966675</v>
+        <v>4.015573978424072</v>
       </c>
       <c r="K17" t="n">
-        <v>4.24615740776062</v>
+        <v>4.766596794128418</v>
       </c>
       <c r="L17" t="n">
-        <v>4.464272165298462</v>
+        <v>4.561196780204773</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>4.347403049468994</v>
+        <v>4.812486886978149</v>
       </c>
       <c r="C18" t="n">
-        <v>4.123506307601929</v>
+        <v>4.962112426757812</v>
       </c>
       <c r="D18" t="n">
-        <v>4.965865135192871</v>
+        <v>4.360176563262939</v>
       </c>
       <c r="E18" t="n">
-        <v>4.668606281280518</v>
+        <v>4.453617095947266</v>
       </c>
       <c r="F18" t="n">
-        <v>4.827425241470337</v>
+        <v>3.993314027786255</v>
       </c>
       <c r="G18" t="n">
-        <v>4.337214231491089</v>
+        <v>4.547442674636841</v>
       </c>
       <c r="H18" t="n">
-        <v>4.449405908584595</v>
+        <v>4.478577375411987</v>
       </c>
       <c r="I18" t="n">
-        <v>5.111208200454712</v>
+        <v>4.69957709312439</v>
       </c>
       <c r="J18" t="n">
-        <v>4.538176298141479</v>
+        <v>5.596759080886841</v>
       </c>
       <c r="K18" t="n">
-        <v>4.46537971496582</v>
+        <v>4.543985366821289</v>
       </c>
       <c r="L18" t="n">
-        <v>4.583419036865235</v>
+        <v>4.644804859161377</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.351656675338745</v>
+        <v>4.464630603790283</v>
       </c>
       <c r="C19" t="n">
-        <v>4.507762908935547</v>
+        <v>4.364893436431885</v>
       </c>
       <c r="D19" t="n">
-        <v>4.224997997283936</v>
+        <v>3.801330327987671</v>
       </c>
       <c r="E19" t="n">
-        <v>4.925666809082031</v>
+        <v>4.555548906326294</v>
       </c>
       <c r="F19" t="n">
-        <v>4.569104194641113</v>
+        <v>4.378876209259033</v>
       </c>
       <c r="G19" t="n">
-        <v>5.385496854782104</v>
+        <v>4.386832237243652</v>
       </c>
       <c r="H19" t="n">
-        <v>4.389596939086914</v>
+        <v>4.078603982925415</v>
       </c>
       <c r="I19" t="n">
-        <v>4.264792680740356</v>
+        <v>4.260718107223511</v>
       </c>
       <c r="J19" t="n">
-        <v>5.033494234085083</v>
+        <v>4.536950826644897</v>
       </c>
       <c r="K19" t="n">
-        <v>4.398780345916748</v>
+        <v>4.182362079620361</v>
       </c>
       <c r="L19" t="n">
-        <v>4.605134963989258</v>
+        <v>4.3010746717453</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>5.166826486587524</v>
+        <v>5.634631395339966</v>
       </c>
       <c r="C20" t="n">
-        <v>4.779300689697266</v>
+        <v>4.768910646438599</v>
       </c>
       <c r="D20" t="n">
-        <v>5.462591409683228</v>
+        <v>5.810206174850464</v>
       </c>
       <c r="E20" t="n">
-        <v>5.310982227325439</v>
+        <v>5.291587352752686</v>
       </c>
       <c r="F20" t="n">
-        <v>5.044168710708618</v>
+        <v>4.561376810073853</v>
       </c>
       <c r="G20" t="n">
-        <v>5.508455276489258</v>
+        <v>4.760416507720947</v>
       </c>
       <c r="H20" t="n">
-        <v>5.285027265548706</v>
+        <v>5.508454084396362</v>
       </c>
       <c r="I20" t="n">
-        <v>5.18680739402771</v>
+        <v>5.173856735229492</v>
       </c>
       <c r="J20" t="n">
-        <v>4.995770215988159</v>
+        <v>4.735642194747925</v>
       </c>
       <c r="K20" t="n">
-        <v>5.397234916687012</v>
+        <v>4.976365089416504</v>
       </c>
       <c r="L20" t="n">
-        <v>5.213716459274292</v>
+        <v>5.12214469909668</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>5.060628414154053</v>
+        <v>4.134293079376221</v>
       </c>
       <c r="C21" t="n">
-        <v>4.237182140350342</v>
+        <v>4.712917566299438</v>
       </c>
       <c r="D21" t="n">
-        <v>4.813729047775269</v>
+        <v>4.97705602645874</v>
       </c>
       <c r="E21" t="n">
-        <v>4.669598817825317</v>
+        <v>4.052460432052612</v>
       </c>
       <c r="F21" t="n">
-        <v>4.721460580825806</v>
+        <v>4.206068992614746</v>
       </c>
       <c r="G21" t="n">
-        <v>4.304538249969482</v>
+        <v>3.945740699768066</v>
       </c>
       <c r="H21" t="n">
-        <v>4.637186050415039</v>
+        <v>5.361575841903687</v>
       </c>
       <c r="I21" t="n">
-        <v>4.751894950866699</v>
+        <v>4.19408917427063</v>
       </c>
       <c r="J21" t="n">
-        <v>4.408753871917725</v>
+        <v>4.815482616424561</v>
       </c>
       <c r="K21" t="n">
-        <v>4.247223377227783</v>
+        <v>3.860479116439819</v>
       </c>
       <c r="L21" t="n">
-        <v>4.585219550132751</v>
+        <v>4.426016354560852</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.55638861656189</v>
+        <v>4.483843088150024</v>
       </c>
       <c r="C22" t="n">
-        <v>4.547893762588501</v>
+        <v>4.281878232955933</v>
       </c>
       <c r="D22" t="n">
-        <v>4.426711082458496</v>
+        <v>5.114293098449707</v>
       </c>
       <c r="E22" t="n">
-        <v>4.31351113319397</v>
+        <v>4.431993246078491</v>
       </c>
       <c r="F22" t="n">
-        <v>4.747400283813477</v>
+        <v>4.316279172897339</v>
       </c>
       <c r="G22" t="n">
-        <v>4.606265068054199</v>
+        <v>4.647911310195923</v>
       </c>
       <c r="H22" t="n">
-        <v>4.40078067779541</v>
+        <v>4.684324741363525</v>
       </c>
       <c r="I22" t="n">
-        <v>4.416729688644409</v>
+        <v>4.462378740310669</v>
       </c>
       <c r="J22" t="n">
-        <v>4.268628358840942</v>
+        <v>4.242697954177856</v>
       </c>
       <c r="K22" t="n">
-        <v>4.724449634552002</v>
+        <v>4.477595567703247</v>
       </c>
       <c r="L22" t="n">
-        <v>4.50087583065033</v>
+        <v>4.514319515228271</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>3.828233003616333</v>
+        <v>4.41576623916626</v>
       </c>
       <c r="C23" t="n">
-        <v>4.656635761260986</v>
+        <v>4.390803337097168</v>
       </c>
       <c r="D23" t="n">
-        <v>4.111032485961914</v>
+        <v>4.101070165634155</v>
       </c>
       <c r="E23" t="n">
-        <v>4.224245071411133</v>
+        <v>4.146458387374878</v>
       </c>
       <c r="F23" t="n">
-        <v>4.803763628005981</v>
+        <v>4.020764827728271</v>
       </c>
       <c r="G23" t="n">
-        <v>4.025743007659912</v>
+        <v>4.569870233535767</v>
       </c>
       <c r="H23" t="n">
-        <v>4.263072967529297</v>
+        <v>3.939967155456543</v>
       </c>
       <c r="I23" t="n">
-        <v>4.714518070220947</v>
+        <v>4.304542779922485</v>
       </c>
       <c r="J23" t="n">
-        <v>4.30914306640625</v>
+        <v>4.000323057174683</v>
       </c>
       <c r="K23" t="n">
-        <v>4.156938314437866</v>
+        <v>4.502535343170166</v>
       </c>
       <c r="L23" t="n">
-        <v>4.309332537651062</v>
+        <v>4.239210152626038</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4.598027944564819</v>
+        <v>4.516029596328735</v>
       </c>
       <c r="C24" t="n">
-        <v>4.684289216995239</v>
+        <v>4.390859842300415</v>
       </c>
       <c r="D24" t="n">
-        <v>4.294807434082031</v>
+        <v>4.705552101135254</v>
       </c>
       <c r="E24" t="n">
-        <v>4.655361890792847</v>
+        <v>4.454657077789307</v>
       </c>
       <c r="F24" t="n">
-        <v>4.582065582275391</v>
+        <v>4.365214824676514</v>
       </c>
       <c r="G24" t="n">
-        <v>4.671835422515869</v>
+        <v>4.498873710632324</v>
       </c>
       <c r="H24" t="n">
-        <v>4.613033771514893</v>
+        <v>4.206299304962158</v>
       </c>
       <c r="I24" t="n">
-        <v>4.732177972793579</v>
+        <v>4.52747368812561</v>
       </c>
       <c r="J24" t="n">
-        <v>4.803521394729614</v>
+        <v>4.520983934402466</v>
       </c>
       <c r="K24" t="n">
-        <v>4.738658905029297</v>
+        <v>4.625260591506958</v>
       </c>
       <c r="L24" t="n">
-        <v>4.637377953529358</v>
+        <v>4.481120467185974</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>4.436458110809326</v>
+        <v>4.420750379562378</v>
       </c>
       <c r="C25" t="n">
-        <v>4.416492462158203</v>
+        <v>4.117023229598999</v>
       </c>
       <c r="D25" t="n">
-        <v>4.631954908370972</v>
+        <v>4.436730861663818</v>
       </c>
       <c r="E25" t="n">
-        <v>4.471879959106445</v>
+        <v>4.441202402114868</v>
       </c>
       <c r="F25" t="n">
-        <v>4.572100400924683</v>
+        <v>4.647193908691406</v>
       </c>
       <c r="G25" t="n">
-        <v>4.806507110595703</v>
+        <v>5.249627590179443</v>
       </c>
       <c r="H25" t="n">
-        <v>4.457666873931885</v>
+        <v>4.515653610229492</v>
       </c>
       <c r="I25" t="n">
-        <v>5.012235879898071</v>
+        <v>4.626954793930054</v>
       </c>
       <c r="J25" t="n">
-        <v>5.015195369720459</v>
+        <v>4.076401948928833</v>
       </c>
       <c r="K25" t="n">
-        <v>4.754417896270752</v>
+        <v>4.63943886756897</v>
       </c>
       <c r="L25" t="n">
-        <v>4.65749089717865</v>
+        <v>4.517097759246826</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.401777982711792</v>
+        <v>4.833853244781494</v>
       </c>
       <c r="C26" t="n">
-        <v>4.310516119003296</v>
+        <v>4.75521993637085</v>
       </c>
       <c r="D26" t="n">
-        <v>4.570340871810913</v>
+        <v>3.994627237319946</v>
       </c>
       <c r="E26" t="n">
-        <v>4.404169082641602</v>
+        <v>3.981644868850708</v>
       </c>
       <c r="F26" t="n">
-        <v>4.665860176086426</v>
+        <v>4.485844373703003</v>
       </c>
       <c r="G26" t="n">
-        <v>4.415495872497559</v>
+        <v>4.816473245620728</v>
       </c>
       <c r="H26" t="n">
-        <v>4.06794285774231</v>
+        <v>4.136456489562988</v>
       </c>
       <c r="I26" t="n">
-        <v>5.210430145263672</v>
+        <v>4.695327520370483</v>
       </c>
       <c r="J26" t="n">
-        <v>4.459656476974487</v>
+        <v>4.275983810424805</v>
       </c>
       <c r="K26" t="n">
-        <v>3.987829208374023</v>
+        <v>4.66586446762085</v>
       </c>
       <c r="L26" t="n">
-        <v>4.449401879310608</v>
+        <v>4.464129519462586</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>3.857650518417358</v>
+        <v>3.997604370117188</v>
       </c>
       <c r="C27" t="n">
-        <v>3.824251174926758</v>
+        <v>3.994609355926514</v>
       </c>
       <c r="D27" t="n">
-        <v>4.714470148086548</v>
+        <v>3.880426168441772</v>
       </c>
       <c r="E27" t="n">
-        <v>4.092070579528809</v>
+        <v>4.138739347457886</v>
       </c>
       <c r="F27" t="n">
-        <v>4.132945775985718</v>
+        <v>3.920335292816162</v>
       </c>
       <c r="G27" t="n">
-        <v>4.111037731170654</v>
+        <v>4.770606756210327</v>
       </c>
       <c r="H27" t="n">
-        <v>4.081111669540405</v>
+        <v>4.301325559616089</v>
       </c>
       <c r="I27" t="n">
-        <v>4.459618330001831</v>
+        <v>3.809719085693359</v>
       </c>
       <c r="J27" t="n">
-        <v>4.075459241867065</v>
+        <v>4.37334418296814</v>
       </c>
       <c r="K27" t="n">
-        <v>4.028521537780762</v>
+        <v>4.81973671913147</v>
       </c>
       <c r="L27" t="n">
-        <v>4.137713670730591</v>
+        <v>4.200644683837891</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.004565238952637</v>
+        <v>4.198318719863892</v>
       </c>
       <c r="C28" t="n">
-        <v>4.541680097579956</v>
+        <v>4.197319984436035</v>
       </c>
       <c r="D28" t="n">
-        <v>4.230014324188232</v>
+        <v>4.296611547470093</v>
       </c>
       <c r="E28" t="n">
-        <v>4.571092844009399</v>
+        <v>3.839205503463745</v>
       </c>
       <c r="F28" t="n">
-        <v>4.814464569091797</v>
+        <v>4.254702568054199</v>
       </c>
       <c r="G28" t="n">
-        <v>4.44443416595459</v>
+        <v>4.416741132736206</v>
       </c>
       <c r="H28" t="n">
-        <v>4.131267786026001</v>
+        <v>4.286590099334717</v>
       </c>
       <c r="I28" t="n">
-        <v>4.357161521911621</v>
+        <v>4.571860551834106</v>
       </c>
       <c r="J28" t="n">
-        <v>4.305278301239014</v>
+        <v>5.016243696212769</v>
       </c>
       <c r="K28" t="n">
-        <v>4.637935400009155</v>
+        <v>4.001842498779297</v>
       </c>
       <c r="L28" t="n">
-        <v>4.403789424896241</v>
+        <v>4.307943630218506</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.254436016082764</v>
+        <v>4.167422771453857</v>
       </c>
       <c r="C29" t="n">
-        <v>4.133727788925171</v>
+        <v>4.020779371261597</v>
       </c>
       <c r="D29" t="n">
-        <v>5.533752202987671</v>
+        <v>3.930482149124146</v>
       </c>
       <c r="E29" t="n">
-        <v>4.141947507858276</v>
+        <v>4.447547674179077</v>
       </c>
       <c r="F29" t="n">
-        <v>4.109026908874512</v>
+        <v>4.155725717544556</v>
       </c>
       <c r="G29" t="n">
-        <v>4.787811279296875</v>
+        <v>4.494829177856445</v>
       </c>
       <c r="H29" t="n">
-        <v>4.205299377441406</v>
+        <v>4.756229400634766</v>
       </c>
       <c r="I29" t="n">
-        <v>4.137964248657227</v>
+        <v>4.750673532485962</v>
       </c>
       <c r="J29" t="n">
-        <v>4.590278625488281</v>
+        <v>4.894786357879639</v>
       </c>
       <c r="K29" t="n">
-        <v>4.158435106277466</v>
+        <v>4.060437679290771</v>
       </c>
       <c r="L29" t="n">
-        <v>4.405267906188965</v>
+        <v>4.367891383171082</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.827701807022095</v>
+        <v>4.156198740005493</v>
       </c>
       <c r="C30" t="n">
-        <v>4.524956941604614</v>
+        <v>4.108908176422119</v>
       </c>
       <c r="D30" t="n">
-        <v>4.529942512512207</v>
+        <v>4.383681774139404</v>
       </c>
       <c r="E30" t="n">
-        <v>4.139477014541626</v>
+        <v>4.259929180145264</v>
       </c>
       <c r="F30" t="n">
-        <v>4.165852308273315</v>
+        <v>4.177162170410156</v>
       </c>
       <c r="G30" t="n">
-        <v>4.304531574249268</v>
+        <v>3.797132253646851</v>
       </c>
       <c r="H30" t="n">
-        <v>4.102043628692627</v>
+        <v>7.989947319030762</v>
       </c>
       <c r="I30" t="n">
-        <v>4.434670448303223</v>
+        <v>6.878145456314087</v>
       </c>
       <c r="J30" t="n">
-        <v>4.013768434524536</v>
+        <v>4.114026784896851</v>
       </c>
       <c r="K30" t="n">
-        <v>4.243689060211182</v>
+        <v>4.289591312408447</v>
       </c>
       <c r="L30" t="n">
-        <v>4.32866337299347</v>
+        <v>4.815472316741944</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>4.420710325241089</v>
+        <v>4.585353136062622</v>
       </c>
       <c r="C31" t="n">
-        <v>5.019218683242798</v>
+        <v>4.737454175949097</v>
       </c>
       <c r="D31" t="n">
-        <v>4.703515529632568</v>
+        <v>4.502042055130005</v>
       </c>
       <c r="E31" t="n">
-        <v>4.858644008636475</v>
+        <v>4.96537971496582</v>
       </c>
       <c r="F31" t="n">
-        <v>6.21724009513855</v>
+        <v>4.604767560958862</v>
       </c>
       <c r="G31" t="n">
-        <v>5.350462436676025</v>
+        <v>4.751898527145386</v>
       </c>
       <c r="H31" t="n">
-        <v>5.171058893203735</v>
+        <v>4.858665704727173</v>
       </c>
       <c r="I31" t="n">
-        <v>4.938144207000732</v>
+        <v>4.523533344268799</v>
       </c>
       <c r="J31" t="n">
-        <v>5.008949756622314</v>
+        <v>4.719507932662964</v>
       </c>
       <c r="K31" t="n">
-        <v>4.927661418914795</v>
+        <v>4.878565549850464</v>
       </c>
       <c r="L31" t="n">
-        <v>5.061560535430909</v>
+        <v>4.712716770172119</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>4.992997884750366</v>
+        <v>4.962388277053833</v>
       </c>
       <c r="C32" t="n">
-        <v>4.627618074417114</v>
+        <v>4.34743332862854</v>
       </c>
       <c r="D32" t="n">
-        <v>5.021946668624878</v>
+        <v>4.539969205856323</v>
       </c>
       <c r="E32" t="n">
-        <v>4.52472710609436</v>
+        <v>4.600039958953857</v>
       </c>
       <c r="F32" t="n">
-        <v>4.597013473510742</v>
+        <v>4.594556093215942</v>
       </c>
       <c r="G32" t="n">
-        <v>5.104220151901245</v>
+        <v>4.387613296508789</v>
       </c>
       <c r="H32" t="n">
-        <v>5.115183591842651</v>
+        <v>4.922688007354736</v>
       </c>
       <c r="I32" t="n">
-        <v>4.782531499862671</v>
+        <v>5.09926700592041</v>
       </c>
       <c r="J32" t="n">
-        <v>4.983518600463867</v>
+        <v>4.805508375167847</v>
       </c>
       <c r="K32" t="n">
-        <v>4.752619743347168</v>
+        <v>4.253455400466919</v>
       </c>
       <c r="L32" t="n">
-        <v>4.850237679481507</v>
+        <v>4.65129189491272</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.480841875076294</v>
+        <v>4.053473949432373</v>
       </c>
       <c r="C33" t="n">
-        <v>5.111188888549805</v>
+        <v>4.708275318145752</v>
       </c>
       <c r="D33" t="n">
-        <v>4.228988409042358</v>
+        <v>4.379943609237671</v>
       </c>
       <c r="E33" t="n">
-        <v>4.519720792770386</v>
+        <v>4.705564022064209</v>
       </c>
       <c r="F33" t="n">
-        <v>5.353586435317993</v>
+        <v>4.304576873779297</v>
       </c>
       <c r="G33" t="n">
-        <v>4.922664880752563</v>
+        <v>4.530949354171753</v>
       </c>
       <c r="H33" t="n">
-        <v>4.468855857849121</v>
+        <v>4.439722537994385</v>
       </c>
       <c r="I33" t="n">
-        <v>4.984032392501831</v>
+        <v>4.411781549453735</v>
       </c>
       <c r="J33" t="n">
-        <v>4.992513418197632</v>
+        <v>5.113486528396606</v>
       </c>
       <c r="K33" t="n">
-        <v>5.790917873382568</v>
+        <v>4.680590867996216</v>
       </c>
       <c r="L33" t="n">
-        <v>4.885331082344055</v>
+        <v>4.5328364610672</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>4.282370328903198</v>
+        <v>4.112044811248779</v>
       </c>
       <c r="C34" t="n">
-        <v>3.982684850692749</v>
+        <v>3.72701621055603</v>
       </c>
       <c r="D34" t="n">
-        <v>4.28186559677124</v>
+        <v>3.954941511154175</v>
       </c>
       <c r="E34" t="n">
-        <v>3.826534271240234</v>
+        <v>3.790372133255005</v>
       </c>
       <c r="F34" t="n">
-        <v>3.920286893844604</v>
+        <v>3.779879093170166</v>
       </c>
       <c r="G34" t="n">
-        <v>3.986619234085083</v>
+        <v>3.785382032394409</v>
       </c>
       <c r="H34" t="n">
-        <v>3.798598766326904</v>
+        <v>4.088253736495972</v>
       </c>
       <c r="I34" t="n">
-        <v>4.466876983642578</v>
+        <v>4.113173246383667</v>
       </c>
       <c r="J34" t="n">
-        <v>3.959686756134033</v>
+        <v>3.76689338684082</v>
       </c>
       <c r="K34" t="n">
-        <v>3.956197738647461</v>
+        <v>3.646224021911621</v>
       </c>
       <c r="L34" t="n">
-        <v>4.046172142028809</v>
+        <v>3.876418018341064</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>3.860465049743652</v>
+        <v>3.721060991287231</v>
       </c>
       <c r="C35" t="n">
-        <v>3.608614683151245</v>
+        <v>3.896589756011963</v>
       </c>
       <c r="D35" t="n">
-        <v>3.615591764450073</v>
+        <v>3.616795539855957</v>
       </c>
       <c r="E35" t="n">
-        <v>3.754740715026855</v>
+        <v>3.613290309906006</v>
       </c>
       <c r="F35" t="n">
-        <v>3.697861671447754</v>
+        <v>3.550796270370483</v>
       </c>
       <c r="G35" t="n">
-        <v>3.661961317062378</v>
+        <v>4.712821960449219</v>
       </c>
       <c r="H35" t="n">
-        <v>3.808095693588257</v>
+        <v>3.678639888763428</v>
       </c>
       <c r="I35" t="n">
-        <v>3.669449329376221</v>
+        <v>3.569961309432983</v>
       </c>
       <c r="J35" t="n">
-        <v>4.336210250854492</v>
+        <v>4.207277297973633</v>
       </c>
       <c r="K35" t="n">
-        <v>3.863442182540894</v>
+        <v>4.466630935668945</v>
       </c>
       <c r="L35" t="n">
-        <v>3.787643265724182</v>
+        <v>3.903386425971985</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>3.853464365005493</v>
+        <v>4.131963968276978</v>
       </c>
       <c r="C36" t="n">
-        <v>5.177997589111328</v>
+        <v>4.32748556137085</v>
       </c>
       <c r="D36" t="n">
-        <v>4.152201652526855</v>
+        <v>4.91998553276062</v>
       </c>
       <c r="E36" t="n">
-        <v>4.242942333221436</v>
+        <v>4.054976463317871</v>
       </c>
       <c r="F36" t="n">
-        <v>4.704247236251831</v>
+        <v>5.147107601165771</v>
       </c>
       <c r="G36" t="n">
-        <v>4.589054822921753</v>
+        <v>4.171163082122803</v>
       </c>
       <c r="H36" t="n">
-        <v>4.366152286529541</v>
+        <v>4.168665885925293</v>
       </c>
       <c r="I36" t="n">
-        <v>4.281392097473145</v>
+        <v>4.574112892150879</v>
       </c>
       <c r="J36" t="n">
-        <v>4.103817462921143</v>
+        <v>4.726219892501831</v>
       </c>
       <c r="K36" t="n">
-        <v>4.391588926315308</v>
+        <v>4.062448263168335</v>
       </c>
       <c r="L36" t="n">
-        <v>4.386285877227783</v>
+        <v>4.428412914276123</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>5.066795349121094</v>
+        <v>4.879314422607422</v>
       </c>
       <c r="C37" t="n">
-        <v>5.021942138671875</v>
+        <v>5.252858638763428</v>
       </c>
       <c r="D37" t="n">
-        <v>5.151605129241943</v>
+        <v>5.09824538230896</v>
       </c>
       <c r="E37" t="n">
-        <v>5.092230558395386</v>
+        <v>4.919723987579346</v>
       </c>
       <c r="F37" t="n">
-        <v>4.836411952972412</v>
+        <v>4.927686452865601</v>
       </c>
       <c r="G37" t="n">
-        <v>4.893757820129395</v>
+        <v>5.430928468704224</v>
       </c>
       <c r="H37" t="n">
-        <v>5.637315273284912</v>
+        <v>5.064331531524658</v>
       </c>
       <c r="I37" t="n">
-        <v>4.751120567321777</v>
+        <v>5.048879623413086</v>
       </c>
       <c r="J37" t="n">
-        <v>4.82048487663269</v>
+        <v>5.722642421722412</v>
       </c>
       <c r="K37" t="n">
-        <v>5.079307794570923</v>
+        <v>4.98704981803894</v>
       </c>
       <c r="L37" t="n">
-        <v>5.035097146034241</v>
+        <v>5.133166074752808</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>4.512753486633301</v>
+        <v>3.822049140930176</v>
       </c>
       <c r="C38" t="n">
-        <v>4.135728359222412</v>
+        <v>3.871926784515381</v>
       </c>
       <c r="D38" t="n">
-        <v>3.952722549438477</v>
+        <v>4.193134546279907</v>
       </c>
       <c r="E38" t="n">
-        <v>3.897343873977661</v>
+        <v>4.31932258605957</v>
       </c>
       <c r="F38" t="n">
-        <v>3.912327527999878</v>
+        <v>3.889396667480469</v>
       </c>
       <c r="G38" t="n">
-        <v>4.01355242729187</v>
+        <v>3.686922073364258</v>
       </c>
       <c r="H38" t="n">
-        <v>3.963203430175781</v>
+        <v>4.389602661132812</v>
       </c>
       <c r="I38" t="n">
-        <v>3.850481271743774</v>
+        <v>4.069419622421265</v>
       </c>
       <c r="J38" t="n">
-        <v>3.877891063690186</v>
+        <v>3.759232759475708</v>
       </c>
       <c r="K38" t="n">
-        <v>4.226514101028442</v>
+        <v>4.036507606506348</v>
       </c>
       <c r="L38" t="n">
-        <v>4.034251809120178</v>
+        <v>4.003751444816589</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>4.316257238388062</v>
+        <v>3.848520994186401</v>
       </c>
       <c r="C39" t="n">
-        <v>4.694280624389648</v>
+        <v>3.890357494354248</v>
       </c>
       <c r="D39" t="n">
-        <v>4.406517267227173</v>
+        <v>4.119030237197876</v>
       </c>
       <c r="E39" t="n">
-        <v>4.287857055664062</v>
+        <v>4.458667755126953</v>
       </c>
       <c r="F39" t="n">
-        <v>4.085868835449219</v>
+        <v>4.053171873092651</v>
       </c>
       <c r="G39" t="n">
-        <v>4.271379470825195</v>
+        <v>3.881215572357178</v>
       </c>
       <c r="H39" t="n">
-        <v>4.191125154495239</v>
+        <v>3.962007761001587</v>
       </c>
       <c r="I39" t="n">
-        <v>4.092354774475098</v>
+        <v>4.665111780166626</v>
       </c>
       <c r="J39" t="n">
-        <v>3.904325485229492</v>
+        <v>3.841725587844849</v>
       </c>
       <c r="K39" t="n">
-        <v>3.99067497253418</v>
+        <v>3.868132352828979</v>
       </c>
       <c r="L39" t="n">
-        <v>4.224064087867736</v>
+        <v>4.058794140815735</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.821444511413574</v>
+        <v>4.559437274932861</v>
       </c>
       <c r="C40" t="n">
-        <v>4.518732309341431</v>
+        <v>4.567340612411499</v>
       </c>
       <c r="D40" t="n">
-        <v>4.403543710708618</v>
+        <v>4.072421789169312</v>
       </c>
       <c r="E40" t="n">
-        <v>4.435956954956055</v>
+        <v>4.851914167404175</v>
       </c>
       <c r="F40" t="n">
-        <v>4.460326433181763</v>
+        <v>4.480364322662354</v>
       </c>
       <c r="G40" t="n">
-        <v>4.359898805618286</v>
+        <v>4.999687671661377</v>
       </c>
       <c r="H40" t="n">
-        <v>4.951869964599609</v>
+        <v>4.492815732955933</v>
       </c>
       <c r="I40" t="n">
-        <v>4.973360776901245</v>
+        <v>4.618980407714844</v>
       </c>
       <c r="J40" t="n">
-        <v>4.480568170547485</v>
+        <v>4.482826232910156</v>
       </c>
       <c r="K40" t="n">
-        <v>4.615239381790161</v>
+        <v>4.253942251205444</v>
       </c>
       <c r="L40" t="n">
-        <v>4.602094101905823</v>
+        <v>4.537973046302795</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.503015995025635</v>
+        <v>4.27640962600708</v>
       </c>
       <c r="C41" t="n">
-        <v>4.310518264770508</v>
+        <v>4.35321044921875</v>
       </c>
       <c r="D41" t="n">
-        <v>4.198294162750244</v>
+        <v>4.659387350082397</v>
       </c>
       <c r="E41" t="n">
-        <v>4.243689775466919</v>
+        <v>4.064961433410645</v>
       </c>
       <c r="F41" t="n">
-        <v>5.485000133514404</v>
+        <v>4.447440624237061</v>
       </c>
       <c r="G41" t="n">
-        <v>4.260640859603882</v>
+        <v>4.531738758087158</v>
       </c>
       <c r="H41" t="n">
-        <v>4.594295024871826</v>
+        <v>4.236014127731323</v>
       </c>
       <c r="I41" t="n">
-        <v>4.642159938812256</v>
+        <v>4.271393537521362</v>
       </c>
       <c r="J41" t="n">
-        <v>4.419719219207764</v>
+        <v>4.454415798187256</v>
       </c>
       <c r="K41" t="n">
-        <v>4.131948471069336</v>
+        <v>4.291848659515381</v>
       </c>
       <c r="L41" t="n">
-        <v>4.478928184509277</v>
+        <v>4.358682036399841</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>4.562372922897339</v>
+        <v>5.105263233184814</v>
       </c>
       <c r="C42" t="n">
-        <v>4.825702905654907</v>
+        <v>4.305323839187622</v>
       </c>
       <c r="D42" t="n">
-        <v>4.567352056503296</v>
+        <v>5.231385469436646</v>
       </c>
       <c r="E42" t="n">
-        <v>4.850628614425659</v>
+        <v>4.750178813934326</v>
       </c>
       <c r="F42" t="n">
-        <v>5.072567224502563</v>
+        <v>4.606005907058716</v>
       </c>
       <c r="G42" t="n">
-        <v>4.672079563140869</v>
+        <v>4.483849763870239</v>
       </c>
       <c r="H42" t="n">
-        <v>4.79179310798645</v>
+        <v>4.490822315216064</v>
       </c>
       <c r="I42" t="n">
-        <v>4.601279973983765</v>
+        <v>4.54369592666626</v>
       </c>
       <c r="J42" t="n">
-        <v>4.466608285903931</v>
+        <v>5.004010677337646</v>
       </c>
       <c r="K42" t="n">
-        <v>4.631736755371094</v>
+        <v>4.413537502288818</v>
       </c>
       <c r="L42" t="n">
-        <v>4.704212141036987</v>
+        <v>4.693407344818115</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.793772220611572</v>
+        <v>4.826461791992188</v>
       </c>
       <c r="C43" t="n">
-        <v>5.038155078887939</v>
+        <v>4.330768346786499</v>
       </c>
       <c r="D43" t="n">
-        <v>4.705504894256592</v>
+        <v>4.726210594177246</v>
       </c>
       <c r="E43" t="n">
-        <v>5.139425992965698</v>
+        <v>4.348197460174561</v>
       </c>
       <c r="F43" t="n">
-        <v>4.811719655990601</v>
+        <v>4.903764724731445</v>
       </c>
       <c r="G43" t="n">
-        <v>4.980356931686401</v>
+        <v>4.571118593215942</v>
       </c>
       <c r="H43" t="n">
-        <v>4.928914546966553</v>
+        <v>5.454077243804932</v>
       </c>
       <c r="I43" t="n">
-        <v>5.117424964904785</v>
+        <v>5.090163707733154</v>
       </c>
       <c r="J43" t="n">
-        <v>4.707497358322144</v>
+        <v>4.383829355239868</v>
       </c>
       <c r="K43" t="n">
-        <v>4.528932332992554</v>
+        <v>5.02522349357605</v>
       </c>
       <c r="L43" t="n">
-        <v>4.875170397758484</v>
+        <v>4.765981531143188</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.372860670089722</v>
+        <v>4.486078500747681</v>
       </c>
       <c r="C44" t="n">
-        <v>4.709485054016113</v>
+        <v>4.506047487258911</v>
       </c>
       <c r="D44" t="n">
-        <v>4.167379140853882</v>
+        <v>4.707520961761475</v>
       </c>
       <c r="E44" t="n">
-        <v>4.208274364471436</v>
+        <v>4.190856695175171</v>
       </c>
       <c r="F44" t="n">
-        <v>4.224225521087646</v>
+        <v>6.810234546661377</v>
       </c>
       <c r="G44" t="n">
-        <v>4.077592134475708</v>
+        <v>4.496085643768311</v>
       </c>
       <c r="H44" t="n">
-        <v>4.561431169509888</v>
+        <v>4.326478242874146</v>
       </c>
       <c r="I44" t="n">
-        <v>4.389459609985352</v>
+        <v>4.07114052772522</v>
       </c>
       <c r="J44" t="n">
-        <v>4.398785829544067</v>
+        <v>4.248185873031616</v>
       </c>
       <c r="K44" t="n">
-        <v>5.047128200531006</v>
+        <v>4.084118843078613</v>
       </c>
       <c r="L44" t="n">
-        <v>4.415662169456482</v>
+        <v>4.592674732208252</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>3.791368722915649</v>
+        <v>4.265142202377319</v>
       </c>
       <c r="C45" t="n">
-        <v>4.867624998092651</v>
+        <v>4.120989084243774</v>
       </c>
       <c r="D45" t="n">
-        <v>3.955908536911011</v>
+        <v>3.770405530929565</v>
       </c>
       <c r="E45" t="n">
-        <v>3.936461448669434</v>
+        <v>4.15092658996582</v>
       </c>
       <c r="F45" t="n">
-        <v>3.854714632034302</v>
+        <v>3.954920768737793</v>
       </c>
       <c r="G45" t="n">
-        <v>4.328752279281616</v>
+        <v>3.694119691848755</v>
       </c>
       <c r="H45" t="n">
-        <v>3.616600513458252</v>
+        <v>4.393836259841919</v>
       </c>
       <c r="I45" t="n">
-        <v>3.959174871444702</v>
+        <v>3.785852670669556</v>
       </c>
       <c r="J45" t="n">
-        <v>3.95612645149231</v>
+        <v>3.944966554641724</v>
       </c>
       <c r="K45" t="n">
-        <v>4.069620609283447</v>
+        <v>3.896596670150757</v>
       </c>
       <c r="L45" t="n">
-        <v>4.033635306358337</v>
+        <v>3.997775602340698</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.760381937026978</v>
+        <v>4.118029117584229</v>
       </c>
       <c r="C46" t="n">
-        <v>4.626220464706421</v>
+        <v>4.536946535110474</v>
       </c>
       <c r="D46" t="n">
-        <v>4.515983581542969</v>
+        <v>4.15641975402832</v>
       </c>
       <c r="E46" t="n">
-        <v>4.133488416671753</v>
+        <v>4.157914400100708</v>
       </c>
       <c r="F46" t="n">
-        <v>4.555873155593872</v>
+        <v>3.938464403152466</v>
       </c>
       <c r="G46" t="n">
-        <v>4.438677310943604</v>
+        <v>4.994307994842529</v>
       </c>
       <c r="H46" t="n">
-        <v>4.757881879806519</v>
+        <v>4.488070726394653</v>
       </c>
       <c r="I46" t="n">
-        <v>4.468584775924683</v>
+        <v>4.187365531921387</v>
       </c>
       <c r="J46" t="n">
-        <v>4.388822078704834</v>
+        <v>4.386881828308105</v>
       </c>
       <c r="K46" t="n">
-        <v>4.129966735839844</v>
+        <v>4.187828302383423</v>
       </c>
       <c r="L46" t="n">
-        <v>4.477588033676147</v>
+        <v>4.315222859382629</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>3.745451688766479</v>
+        <v>3.94550085067749</v>
       </c>
       <c r="C47" t="n">
-        <v>4.96284031867981</v>
+        <v>5.272089004516602</v>
       </c>
       <c r="D47" t="n">
-        <v>3.558929920196533</v>
+        <v>4.517993211746216</v>
       </c>
       <c r="E47" t="n">
-        <v>4.00378680229187</v>
+        <v>3.979285955429077</v>
       </c>
       <c r="F47" t="n">
-        <v>4.254170656204224</v>
+        <v>3.776209354400635</v>
       </c>
       <c r="G47" t="n">
-        <v>3.612779140472412</v>
+        <v>3.691924333572388</v>
       </c>
       <c r="H47" t="n">
-        <v>3.94545841217041</v>
+        <v>4.389577627182007</v>
       </c>
       <c r="I47" t="n">
-        <v>3.739495515823364</v>
+        <v>3.70688271522522</v>
       </c>
       <c r="J47" t="n">
-        <v>3.693102598190308</v>
+        <v>4.256925821304321</v>
       </c>
       <c r="K47" t="n">
-        <v>3.703054428100586</v>
+        <v>3.912359952926636</v>
       </c>
       <c r="L47" t="n">
-        <v>3.9219069480896</v>
+        <v>4.144874882698059</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.595769643783569</v>
+        <v>4.617514371871948</v>
       </c>
       <c r="C48" t="n">
-        <v>5.126924991607666</v>
+        <v>4.328249931335449</v>
       </c>
       <c r="D48" t="n">
-        <v>4.676065683364868</v>
+        <v>4.450472354888916</v>
       </c>
       <c r="E48" t="n">
-        <v>5.081548452377319</v>
+        <v>4.588079452514648</v>
       </c>
       <c r="F48" t="n">
-        <v>4.795809745788574</v>
+        <v>5.013031005859375</v>
       </c>
       <c r="G48" t="n">
-        <v>4.797750949859619</v>
+        <v>4.711132049560547</v>
       </c>
       <c r="H48" t="n">
-        <v>4.59627366065979</v>
+        <v>4.717543840408325</v>
       </c>
       <c r="I48" t="n">
-        <v>4.845656871795654</v>
+        <v>4.332461357116699</v>
       </c>
       <c r="J48" t="n">
-        <v>5.163345336914062</v>
+        <v>4.485124588012695</v>
       </c>
       <c r="K48" t="n">
-        <v>4.54840350151062</v>
+        <v>4.708517551422119</v>
       </c>
       <c r="L48" t="n">
-        <v>4.822754883766175</v>
+        <v>4.595212650299072</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>5.040164232254028</v>
+        <v>4.583343267440796</v>
       </c>
       <c r="C49" t="n">
-        <v>4.306511163711548</v>
+        <v>4.776837348937988</v>
       </c>
       <c r="D49" t="n">
-        <v>5.028185844421387</v>
+        <v>4.31850528717041</v>
       </c>
       <c r="E49" t="n">
-        <v>4.755894422531128</v>
+        <v>4.269124031066895</v>
       </c>
       <c r="F49" t="n">
-        <v>5.004260301589966</v>
+        <v>5.287051439285278</v>
       </c>
       <c r="G49" t="n">
-        <v>4.137784004211426</v>
+        <v>4.534949779510498</v>
       </c>
       <c r="H49" t="n">
-        <v>4.521966218948364</v>
+        <v>4.288572788238525</v>
       </c>
       <c r="I49" t="n">
-        <v>5.070077657699585</v>
+        <v>4.54702353477478</v>
       </c>
       <c r="J49" t="n">
-        <v>4.207273960113525</v>
+        <v>4.053189277648926</v>
       </c>
       <c r="K49" t="n">
-        <v>4.191318988800049</v>
+        <v>4.691568613052368</v>
       </c>
       <c r="L49" t="n">
-        <v>4.626343679428101</v>
+        <v>4.535016536712646</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.871615886688232</v>
+        <v>3.757938861846924</v>
       </c>
       <c r="C50" t="n">
-        <v>4.442698001861572</v>
+        <v>4.317502737045288</v>
       </c>
       <c r="D50" t="n">
-        <v>3.957908391952515</v>
+        <v>3.841736793518066</v>
       </c>
       <c r="E50" t="n">
-        <v>3.925495386123657</v>
+        <v>3.945449113845825</v>
       </c>
       <c r="F50" t="n">
-        <v>3.947444200515747</v>
+        <v>4.096080780029297</v>
       </c>
       <c r="G50" t="n">
-        <v>3.847684621810913</v>
+        <v>3.903554916381836</v>
       </c>
       <c r="H50" t="n">
-        <v>4.387333393096924</v>
+        <v>4.143963575363159</v>
       </c>
       <c r="I50" t="n">
-        <v>3.89955472946167</v>
+        <v>3.924534320831299</v>
       </c>
       <c r="J50" t="n">
-        <v>4.292913675308228</v>
+        <v>3.725535154342651</v>
       </c>
       <c r="K50" t="n">
-        <v>3.848471403121948</v>
+        <v>3.941476583480835</v>
       </c>
       <c r="L50" t="n">
-        <v>4.04211196899414</v>
+        <v>3.959777283668518</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.17562460899353</v>
+        <v>4.59329891204834</v>
       </c>
       <c r="C51" t="n">
-        <v>4.619969129562378</v>
+        <v>4.640194654464722</v>
       </c>
       <c r="D51" t="n">
-        <v>4.540206670761108</v>
+        <v>4.477129220962524</v>
       </c>
       <c r="E51" t="n">
-        <v>4.355148077011108</v>
+        <v>4.348426818847656</v>
       </c>
       <c r="F51" t="n">
-        <v>5.358058929443359</v>
+        <v>5.111492872238159</v>
       </c>
       <c r="G51" t="n">
-        <v>4.941662549972534</v>
+        <v>4.619235038757324</v>
       </c>
       <c r="H51" t="n">
-        <v>4.119768381118774</v>
+        <v>4.397817611694336</v>
       </c>
       <c r="I51" t="n">
-        <v>5.015940427780151</v>
+        <v>4.130090951919556</v>
       </c>
       <c r="J51" t="n">
-        <v>4.550640821456909</v>
+        <v>4.011772394180298</v>
       </c>
       <c r="K51" t="n">
-        <v>4.086840867996216</v>
+        <v>5.079611301422119</v>
       </c>
       <c r="L51" t="n">
-        <v>4.576386046409607</v>
+        <v>4.540906977653504</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.40692789554596</v>
+        <v>4.412070608139038</v>
       </c>
       <c r="C52" t="n">
-        <v>4.482721438407898</v>
+        <v>4.388673896789551</v>
       </c>
       <c r="D52" t="n">
-        <v>4.450904259681701</v>
+        <v>4.357389698028564</v>
       </c>
       <c r="E52" t="n">
-        <v>4.446944704055786</v>
+        <v>4.339975180625916</v>
       </c>
       <c r="F52" t="n">
-        <v>4.536810688972473</v>
+        <v>4.428368511199952</v>
       </c>
       <c r="G52" t="n">
-        <v>4.446248674392701</v>
+        <v>4.409434370994568</v>
       </c>
       <c r="H52" t="n">
-        <v>4.485208897590637</v>
+        <v>4.604814028739929</v>
       </c>
       <c r="I52" t="n">
-        <v>4.479649357795715</v>
+        <v>4.40392870426178</v>
       </c>
       <c r="J52" t="n">
-        <v>4.412117872238159</v>
+        <v>4.371243529319763</v>
       </c>
       <c r="K52" t="n">
-        <v>4.420862493515014</v>
+        <v>4.391580567359925</v>
       </c>
       <c r="L52" t="n">
-        <v>4.456839628219604</v>
+        <v>4.410747909545899</v>
       </c>
     </row>
   </sheetData>
